--- a/Results_experiment/exp_1/preds_3364444555550000.xlsx
+++ b/Results_experiment/exp_1/preds_3364444555550000.xlsx
@@ -1443,7 +1443,7 @@
         <v>-0.699999988079071</v>
       </c>
       <c r="D2">
-        <v>0.2060436010360718</v>
+        <v>-0.1057146489620209</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1457,7 +1457,7 @@
         <v>12.30000019073486</v>
       </c>
       <c r="D3">
-        <v>8.994977951049805</v>
+        <v>10.52698612213135</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1471,7 +1471,7 @@
         <v>6.099999904632568</v>
       </c>
       <c r="D4">
-        <v>1.668382287025452</v>
+        <v>0.9176235198974609</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1485,7 +1485,7 @@
         <v>6.199999809265137</v>
       </c>
       <c r="D5">
-        <v>1.525876641273499</v>
+        <v>1.025439023971558</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1499,7 +1499,7 @@
         <v>6.900000095367432</v>
       </c>
       <c r="D6">
-        <v>-2.783008098602295</v>
+        <v>-1.938814520835876</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1513,7 +1513,7 @@
         <v>-5.099999904632568</v>
       </c>
       <c r="D7">
-        <v>-2.54062032699585</v>
+        <v>-1.559011936187744</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1527,7 +1527,7 @@
         <v>-18</v>
       </c>
       <c r="D8">
-        <v>-0.0815836489200592</v>
+        <v>0.7541000843048096</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1541,7 +1541,7 @@
         <v>-33.70000076293945</v>
       </c>
       <c r="D9">
-        <v>-24.57135581970215</v>
+        <v>-22.72105026245117</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1555,7 +1555,7 @@
         <v>-24.39999961853027</v>
       </c>
       <c r="D10">
-        <v>-12.45730113983154</v>
+        <v>-14.3703031539917</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1569,7 +1569,7 @@
         <v>-12</v>
       </c>
       <c r="D11">
-        <v>-7.603250026702881</v>
+        <v>-5.725913047790527</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1583,7 +1583,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D12">
-        <v>1.801094889640808</v>
+        <v>-0.9817416667938232</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1597,7 +1597,7 @@
         <v>-19.60000038146973</v>
       </c>
       <c r="D13">
-        <v>-16.60336685180664</v>
+        <v>-17.11403274536133</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1611,7 +1611,7 @@
         <v>-1.600000023841858</v>
       </c>
       <c r="D14">
-        <v>-0.4554923176765442</v>
+        <v>-0.808441162109375</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1625,7 +1625,7 @@
         <v>-0.699999988079071</v>
       </c>
       <c r="D15">
-        <v>0.01903688907623291</v>
+        <v>-0.5507833957672119</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1639,7 +1639,7 @@
         <v>20.60000038146973</v>
       </c>
       <c r="D16">
-        <v>5.565884590148926</v>
+        <v>4.834139823913574</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -1653,7 +1653,7 @@
         <v>-9.5</v>
       </c>
       <c r="D17">
-        <v>-6.539465427398682</v>
+        <v>-7.70585823059082</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -1667,7 +1667,7 @@
         <v>8.300000190734863</v>
       </c>
       <c r="D18">
-        <v>13.14176559448242</v>
+        <v>10.9871940612793</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -1681,7 +1681,7 @@
         <v>-0.8999999761581421</v>
       </c>
       <c r="D19">
-        <v>0.7999075651168823</v>
+        <v>0.2980439960956573</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -1695,7 +1695,7 @@
         <v>-2.700000047683716</v>
       </c>
       <c r="D20">
-        <v>-2.181000232696533</v>
+        <v>-3.276683568954468</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -1709,7 +1709,7 @@
         <v>-14</v>
       </c>
       <c r="D21">
-        <v>-9.191678047180176</v>
+        <v>-10.66732501983643</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -1723,7 +1723,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D22">
-        <v>1.243828415870667</v>
+        <v>0.4648971259593964</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -1737,7 +1737,7 @@
         <v>-12.39999961853027</v>
       </c>
       <c r="D23">
-        <v>-8.796321868896484</v>
+        <v>-8.930222511291504</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -1751,7 +1751,7 @@
         <v>-13.69999980926514</v>
       </c>
       <c r="D24">
-        <v>-7.451560974121094</v>
+        <v>-7.752539157867432</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -1765,7 +1765,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D25">
-        <v>2.198522090911865</v>
+        <v>3.000216722488403</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -1779,7 +1779,7 @@
         <v>-1.600000023841858</v>
       </c>
       <c r="D26">
-        <v>1.369714140892029</v>
+        <v>1.437975287437439</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -1793,7 +1793,7 @@
         <v>3</v>
       </c>
       <c r="D27">
-        <v>-8.74564266204834</v>
+        <v>-8.412999153137207</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -1807,7 +1807,7 @@
         <v>-0.300000011920929</v>
       </c>
       <c r="D28">
-        <v>-1.676103234291077</v>
+        <v>-0.9045079946517944</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -1821,7 +1821,7 @@
         <v>-2.700000047683716</v>
       </c>
       <c r="D29">
-        <v>-3.681896209716797</v>
+        <v>-3.356044054031372</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -1835,7 +1835,7 @@
         <v>-18.79999923706055</v>
       </c>
       <c r="D30">
-        <v>-7.967067241668701</v>
+        <v>-8.03983211517334</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -1849,7 +1849,7 @@
         <v>-1.600000023841858</v>
       </c>
       <c r="D31">
-        <v>1.170239686965942</v>
+        <v>-0.2165034711360931</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -1863,7 +1863,7 @@
         <v>10.89999961853027</v>
       </c>
       <c r="D32">
-        <v>5.287953853607178</v>
+        <v>4.995651721954346</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -1877,7 +1877,7 @@
         <v>-23.10000038146973</v>
       </c>
       <c r="D33">
-        <v>-17.44452285766602</v>
+        <v>-19.3517894744873</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -1891,7 +1891,7 @@
         <v>-19.39999961853027</v>
       </c>
       <c r="D34">
-        <v>-18.72136878967285</v>
+        <v>-19.80294036865234</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -1905,7 +1905,7 @@
         <v>-9.5</v>
       </c>
       <c r="D35">
-        <v>-1.771569490432739</v>
+        <v>-2.005947113037109</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -1919,7 +1919,7 @@
         <v>-1.5</v>
       </c>
       <c r="D36">
-        <v>-5.184534072875977</v>
+        <v>-5.207988739013672</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -1933,7 +1933,7 @@
         <v>-6.699999809265137</v>
       </c>
       <c r="D37">
-        <v>-4.831154346466064</v>
+        <v>-5.558628559112549</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -1947,7 +1947,7 @@
         <v>-5.5</v>
       </c>
       <c r="D38">
-        <v>-0.2727166414260864</v>
+        <v>-1.466628074645996</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -1961,7 +1961,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D39">
-        <v>4.263460159301758</v>
+        <v>2.372047662734985</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -1975,7 +1975,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D40">
-        <v>3.78532600402832</v>
+        <v>2.049701690673828</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -1989,7 +1989,7 @@
         <v>-5.400000095367432</v>
       </c>
       <c r="D41">
-        <v>-3.149838447570801</v>
+        <v>-3.234748601913452</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2003,7 +2003,7 @@
         <v>-16.70000076293945</v>
       </c>
       <c r="D42">
-        <v>-9.677422523498535</v>
+        <v>-12.09530830383301</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2017,7 +2017,7 @@
         <v>-3.5</v>
       </c>
       <c r="D43">
-        <v>0.9031840562820435</v>
+        <v>0.6730260848999023</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2031,7 +2031,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D44">
-        <v>-2.254322528839111</v>
+        <v>1.800071716308594</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2045,7 +2045,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D45">
-        <v>-7.939067840576172</v>
+        <v>-6.789158821105957</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2059,7 +2059,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D46">
-        <v>2.214967250823975</v>
+        <v>1.356053471565247</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2073,7 +2073,7 @@
         <v>-3.5</v>
       </c>
       <c r="D47">
-        <v>0.05562436580657959</v>
+        <v>-0.4293721318244934</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2087,7 +2087,7 @@
         <v>-12.19999980926514</v>
       </c>
       <c r="D48">
-        <v>-1.839793682098389</v>
+        <v>-2.498438596725464</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2101,7 +2101,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D49">
-        <v>-0.430820107460022</v>
+        <v>-0.188164621591568</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2115,7 +2115,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D50">
-        <v>0.07226479053497314</v>
+        <v>-0.9813418388366699</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2129,7 +2129,7 @@
         <v>6.099999904632568</v>
       </c>
       <c r="D51">
-        <v>4.465678215026855</v>
+        <v>4.661632537841797</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2143,7 +2143,7 @@
         <v>-2.200000047683716</v>
       </c>
       <c r="D52">
-        <v>-2.238951206207275</v>
+        <v>-2.816848039627075</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2157,7 +2157,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D53">
-        <v>-1.236741662025452</v>
+        <v>-2.005630970001221</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2171,7 +2171,7 @@
         <v>-13.30000019073486</v>
       </c>
       <c r="D54">
-        <v>-9.136231422424316</v>
+        <v>-9.947846412658691</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2185,7 +2185,7 @@
         <v>3.5</v>
       </c>
       <c r="D55">
-        <v>1.178441166877747</v>
+        <v>0.3403328955173492</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2199,7 +2199,7 @@
         <v>-20.20000076293945</v>
       </c>
       <c r="D56">
-        <v>-17.43245697021484</v>
+        <v>-17.46943664550781</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2213,7 +2213,7 @@
         <v>-1.100000023841858</v>
       </c>
       <c r="D57">
-        <v>0.6399171352386475</v>
+        <v>-0.2965289950370789</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2227,7 +2227,7 @@
         <v>-9.600000381469727</v>
       </c>
       <c r="D58">
-        <v>-6.046080589294434</v>
+        <v>-8.859310150146484</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2241,7 +2241,7 @@
         <v>29.79999923706055</v>
       </c>
       <c r="D59">
-        <v>13.95255565643311</v>
+        <v>14.82691764831543</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2255,7 +2255,7 @@
         <v>-13.19999980926514</v>
       </c>
       <c r="D60">
-        <v>-3.907273769378662</v>
+        <v>-6.083162307739258</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2269,7 +2269,7 @@
         <v>-5.800000190734863</v>
       </c>
       <c r="D61">
-        <v>-2.889100074768066</v>
+        <v>1.504418253898621</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2283,7 +2283,7 @@
         <v>-16.10000038146973</v>
       </c>
       <c r="D62">
-        <v>-5.653453826904297</v>
+        <v>-6.253879547119141</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2297,7 +2297,7 @@
         <v>-1</v>
       </c>
       <c r="D63">
-        <v>-1.568807005882263</v>
+        <v>-1.891419410705566</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2311,7 +2311,7 @@
         <v>-17.39999961853027</v>
       </c>
       <c r="D64">
-        <v>-10.81232643127441</v>
+        <v>-10.57873630523682</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2325,7 +2325,7 @@
         <v>-3.200000047683716</v>
       </c>
       <c r="D65">
-        <v>0.261796772480011</v>
+        <v>-0.3312056362628937</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2339,7 +2339,7 @@
         <v>-14.80000019073486</v>
       </c>
       <c r="D66">
-        <v>-8.695159912109375</v>
+        <v>-10.10189247131348</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2353,7 +2353,7 @@
         <v>5</v>
       </c>
       <c r="D67">
-        <v>0.835085391998291</v>
+        <v>0.6454516649246216</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2367,7 +2367,7 @@
         <v>-19.79999923706055</v>
       </c>
       <c r="D68">
-        <v>-15.8481273651123</v>
+        <v>-17.70734024047852</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2381,7 +2381,7 @@
         <v>-2.799999952316284</v>
       </c>
       <c r="D69">
-        <v>0.2189053893089294</v>
+        <v>0.1667292416095734</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2395,7 +2395,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D70">
-        <v>-3.140348434448242</v>
+        <v>-3.299066543579102</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2409,7 +2409,7 @@
         <v>-0.800000011920929</v>
       </c>
       <c r="D71">
-        <v>-3.592912197113037</v>
+        <v>-4.748942375183105</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2423,7 +2423,7 @@
         <v>9.300000190734863</v>
       </c>
       <c r="D72">
-        <v>5.285779476165771</v>
+        <v>6.001933097839355</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2437,7 +2437,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D73">
-        <v>-1.291850566864014</v>
+        <v>-0.8443218469619751</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2451,7 +2451,7 @@
         <v>15.30000019073486</v>
       </c>
       <c r="D74">
-        <v>9.295441627502441</v>
+        <v>8.066363334655762</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2465,7 +2465,7 @@
         <v>-9.199999809265137</v>
       </c>
       <c r="D75">
-        <v>-6.431689262390137</v>
+        <v>-6.582056045532227</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2479,7 +2479,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D76">
-        <v>-2.828364372253418</v>
+        <v>-3.552558183670044</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2493,7 +2493,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D77">
-        <v>0.2296464443206787</v>
+        <v>-0.2076563835144043</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2507,7 +2507,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D78">
-        <v>-5.64654541015625</v>
+        <v>-5.373386383056641</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2521,7 +2521,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D79">
-        <v>-1.077194571495056</v>
+        <v>-0.5110356211662292</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2535,7 +2535,7 @@
         <v>-11.30000019073486</v>
       </c>
       <c r="D80">
-        <v>-9.069789886474609</v>
+        <v>-10.54946231842041</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2549,7 +2549,7 @@
         <v>-21.29999923706055</v>
       </c>
       <c r="D81">
-        <v>-4.136529922485352</v>
+        <v>-7.515415668487549</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2563,7 +2563,7 @@
         <v>8.800000190734863</v>
       </c>
       <c r="D82">
-        <v>5.159482479095459</v>
+        <v>5.82636833190918</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2577,7 +2577,7 @@
         <v>-10.39999961853027</v>
       </c>
       <c r="D83">
-        <v>-6.645237922668457</v>
+        <v>-8.749959945678711</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -2591,7 +2591,7 @@
         <v>-20.39999961853027</v>
       </c>
       <c r="D84">
-        <v>-17.3560962677002</v>
+        <v>-19.73047637939453</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -2605,7 +2605,7 @@
         <v>-1.700000047683716</v>
       </c>
       <c r="D85">
-        <v>-1.31374979019165</v>
+        <v>-0.5804411172866821</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -2619,7 +2619,7 @@
         <v>-8.399999618530273</v>
       </c>
       <c r="D86">
-        <v>-5.056877613067627</v>
+        <v>-5.657121181488037</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -2633,7 +2633,7 @@
         <v>-1.600000023841858</v>
       </c>
       <c r="D87">
-        <v>-0.7051140666007996</v>
+        <v>-6.381299018859863</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -2647,7 +2647,7 @@
         <v>-6.099999904632568</v>
       </c>
       <c r="D88">
-        <v>-1.796809196472168</v>
+        <v>-1.460799217224121</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -2661,7 +2661,7 @@
         <v>11.69999980926514</v>
       </c>
       <c r="D89">
-        <v>9.050729751586914</v>
+        <v>9.735054016113281</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -2675,7 +2675,7 @@
         <v>8.399999618530273</v>
       </c>
       <c r="D90">
-        <v>2.88254976272583</v>
+        <v>2.620058298110962</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -2689,7 +2689,7 @@
         <v>13.69999980926514</v>
       </c>
       <c r="D91">
-        <v>3.855094432830811</v>
+        <v>1.625201225280762</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -2703,7 +2703,7 @@
         <v>-0.8999999761581421</v>
       </c>
       <c r="D92">
-        <v>-7.456570625305176</v>
+        <v>-7.221837043762207</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -2717,7 +2717,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D93">
-        <v>-1.438035130500793</v>
+        <v>-3.051314830780029</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -2731,7 +2731,7 @@
         <v>4.099999904632568</v>
       </c>
       <c r="D94">
-        <v>2.054821968078613</v>
+        <v>0.5778210163116455</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -2745,7 +2745,7 @@
         <v>-5.5</v>
       </c>
       <c r="D95">
-        <v>-3.912606239318848</v>
+        <v>-4.13031530380249</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -2759,7 +2759,7 @@
         <v>-3.900000095367432</v>
       </c>
       <c r="D96">
-        <v>-1.752972722053528</v>
+        <v>-1.139042615890503</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -2773,7 +2773,7 @@
         <v>0</v>
       </c>
       <c r="D97">
-        <v>1.062267899513245</v>
+        <v>0.4248509109020233</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -2787,7 +2787,7 @@
         <v>6</v>
       </c>
       <c r="D98">
-        <v>1.173200249671936</v>
+        <v>0.5357213020324707</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -2801,7 +2801,7 @@
         <v>-1.200000047683716</v>
       </c>
       <c r="D99">
-        <v>-0.9636722803115845</v>
+        <v>-0.8024365901947021</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -2815,7 +2815,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D100">
-        <v>-5.002676963806152</v>
+        <v>-6.015062808990479</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -2829,7 +2829,7 @@
         <v>-2.200000047683716</v>
       </c>
       <c r="D101">
-        <v>1.663512587547302</v>
+        <v>2.916220903396606</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -2843,7 +2843,7 @@
         <v>-7.199999809265137</v>
       </c>
       <c r="D102">
-        <v>-1.895827889442444</v>
+        <v>-1.327340245246887</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -2857,7 +2857,7 @@
         <v>21.89999961853027</v>
       </c>
       <c r="D103">
-        <v>15.35304355621338</v>
+        <v>14.48982334136963</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -2871,7 +2871,7 @@
         <v>-1.899999976158142</v>
       </c>
       <c r="D104">
-        <v>1.243448257446289</v>
+        <v>0.5624080896377563</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -2885,7 +2885,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D105">
-        <v>0.2470753788948059</v>
+        <v>-0.07454749941825867</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -2899,7 +2899,7 @@
         <v>-1.299999952316284</v>
       </c>
       <c r="D106">
-        <v>0.8942759037017822</v>
+        <v>0.4257673323154449</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -2913,7 +2913,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D107">
-        <v>-0.4355711042881012</v>
+        <v>0.2502420246601105</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -2927,7 +2927,7 @@
         <v>-19</v>
       </c>
       <c r="D108">
-        <v>-17.23755264282227</v>
+        <v>-16.81748199462891</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -2941,7 +2941,7 @@
         <v>-0.300000011920929</v>
       </c>
       <c r="D109">
-        <v>-1.858698964118958</v>
+        <v>-2.85514497756958</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -2955,7 +2955,7 @@
         <v>-1.600000023841858</v>
       </c>
       <c r="D110">
-        <v>-7.214704513549805</v>
+        <v>-7.277095794677734</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -2969,7 +2969,7 @@
         <v>-1.299999952316284</v>
       </c>
       <c r="D111">
-        <v>0.6881998777389526</v>
+        <v>-2.080028057098389</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -2983,7 +2983,7 @@
         <v>-3.799999952316284</v>
       </c>
       <c r="D112">
-        <v>-0.06701812148094177</v>
+        <v>-0.3677638173103333</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -2997,7 +2997,7 @@
         <v>1.5</v>
       </c>
       <c r="D113">
-        <v>0.5916796922683716</v>
+        <v>-0.7985068559646606</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3011,7 +3011,7 @@
         <v>4</v>
       </c>
       <c r="D114">
-        <v>0.9955497980117798</v>
+        <v>-0.07396939396858215</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3025,7 +3025,7 @@
         <v>-11.60000038146973</v>
       </c>
       <c r="D115">
-        <v>-2.091427803039551</v>
+        <v>-2.377326965332031</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3039,7 +3039,7 @@
         <v>-13.5</v>
       </c>
       <c r="D116">
-        <v>-10.13697147369385</v>
+        <v>-9.894309043884277</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3053,7 +3053,7 @@
         <v>-14</v>
       </c>
       <c r="D117">
-        <v>-7.740809917449951</v>
+        <v>-10.53167057037354</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3067,7 +3067,7 @@
         <v>9.899999618530273</v>
       </c>
       <c r="D118">
-        <v>3.299594402313232</v>
+        <v>2.109217643737793</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3081,7 +3081,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D119">
-        <v>1.664914727210999</v>
+        <v>0.9308183193206787</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3095,7 +3095,7 @@
         <v>-7.099999904632568</v>
       </c>
       <c r="D120">
-        <v>0.02503871917724609</v>
+        <v>0.02751922607421875</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3109,7 +3109,7 @@
         <v>5.599999904632568</v>
       </c>
       <c r="D121">
-        <v>1.238296031951904</v>
+        <v>0.7653050422668457</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3123,7 +3123,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D122">
-        <v>3.496175289154053</v>
+        <v>2.438257455825806</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3137,7 +3137,7 @@
         <v>-1.100000023841858</v>
       </c>
       <c r="D123">
-        <v>-1.118894577026367</v>
+        <v>-0.4785691201686859</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3151,7 +3151,7 @@
         <v>-17.39999961853027</v>
       </c>
       <c r="D124">
-        <v>-15.50695419311523</v>
+        <v>-17.11754417419434</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3165,7 +3165,7 @@
         <v>-10.60000038146973</v>
       </c>
       <c r="D125">
-        <v>-8.861279487609863</v>
+        <v>-10.83278942108154</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3179,7 +3179,7 @@
         <v>14.89999961853027</v>
       </c>
       <c r="D126">
-        <v>13.14424324035645</v>
+        <v>9.267810821533203</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3193,7 +3193,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D127">
-        <v>3.154793739318848</v>
+        <v>3.315843820571899</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3207,7 +3207,7 @@
         <v>-0.800000011920929</v>
       </c>
       <c r="D128">
-        <v>-0.3877925872802734</v>
+        <v>-0.382333904504776</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3221,7 +3221,7 @@
         <v>6.400000095367432</v>
       </c>
       <c r="D129">
-        <v>0.60898756980896</v>
+        <v>1.09223461151123</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3235,7 +3235,7 @@
         <v>2.700000047683716</v>
       </c>
       <c r="D130">
-        <v>-1.621592402458191</v>
+        <v>-1.406169295310974</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3249,7 +3249,7 @@
         <v>-2.400000095367432</v>
       </c>
       <c r="D131">
-        <v>-1.393617033958435</v>
+        <v>-1.196861743927002</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3263,7 +3263,7 @@
         <v>-3.200000047683716</v>
       </c>
       <c r="D132">
-        <v>-3.680032253265381</v>
+        <v>-5.595765113830566</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3277,7 +3277,7 @@
         <v>-19.70000076293945</v>
       </c>
       <c r="D133">
-        <v>-15.24799919128418</v>
+        <v>-16.52349853515625</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3291,7 +3291,7 @@
         <v>-1.899999976158142</v>
       </c>
       <c r="D134">
-        <v>-1.764814019203186</v>
+        <v>-1.723695993423462</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3305,7 +3305,7 @@
         <v>-10</v>
       </c>
       <c r="D135">
-        <v>-2.389461040496826</v>
+        <v>-5.827611923217773</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3319,7 +3319,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D136">
-        <v>-0.4570061564445496</v>
+        <v>-0.1497302055358887</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3333,7 +3333,7 @@
         <v>-3.099999904632568</v>
       </c>
       <c r="D137">
-        <v>-2.069254159927368</v>
+        <v>-0.9863749742507935</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3347,7 +3347,7 @@
         <v>8.899999618530273</v>
       </c>
       <c r="D138">
-        <v>-0.1020891666412354</v>
+        <v>-0.1533639430999756</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3361,7 +3361,7 @@
         <v>-4.800000190734863</v>
       </c>
       <c r="D139">
-        <v>-1.638419151306152</v>
+        <v>-2.463290929794312</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3375,7 +3375,7 @@
         <v>-8.399999618530273</v>
       </c>
       <c r="D140">
-        <v>-4.614456176757812</v>
+        <v>-1.915982246398926</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3389,7 +3389,7 @@
         <v>12.89999961853027</v>
       </c>
       <c r="D141">
-        <v>0.5247513055801392</v>
+        <v>-0.5798305869102478</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3403,7 +3403,7 @@
         <v>-21.20000076293945</v>
       </c>
       <c r="D142">
-        <v>-11.88368988037109</v>
+        <v>-17.056884765625</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3417,7 +3417,7 @@
         <v>2.5</v>
       </c>
       <c r="D143">
-        <v>1.03425920009613</v>
+        <v>0.008255422115325928</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3431,7 +3431,7 @@
         <v>-25.89999961853027</v>
       </c>
       <c r="D144">
-        <v>-10.58257865905762</v>
+        <v>-13.61923122406006</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3445,7 +3445,7 @@
         <v>4.800000190734863</v>
       </c>
       <c r="D145">
-        <v>2.869126796722412</v>
+        <v>1.028544425964355</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3459,7 +3459,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D146">
-        <v>2.451523303985596</v>
+        <v>0.58404541015625</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3473,7 +3473,7 @@
         <v>-19.29999923706055</v>
       </c>
       <c r="D147">
-        <v>-5.380109786987305</v>
+        <v>-10.01393795013428</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3487,7 +3487,7 @@
         <v>-8.899999618530273</v>
       </c>
       <c r="D148">
-        <v>-5.811305046081543</v>
+        <v>-4.447632312774658</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3501,7 +3501,7 @@
         <v>-10</v>
       </c>
       <c r="D149">
-        <v>-6.329810619354248</v>
+        <v>-6.749542236328125</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3515,7 +3515,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D150">
-        <v>-8.349055290222168</v>
+        <v>-9.009496688842773</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3529,7 +3529,7 @@
         <v>7.800000190734863</v>
       </c>
       <c r="D151">
-        <v>2.262945652008057</v>
+        <v>1.500550031661987</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3543,7 +3543,7 @@
         <v>-4.5</v>
       </c>
       <c r="D152">
-        <v>0.3829456567764282</v>
+        <v>0.1333218514919281</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3557,7 +3557,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D153">
-        <v>-0.8081563711166382</v>
+        <v>-1.128266215324402</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3571,7 +3571,7 @@
         <v>-1.200000047683716</v>
       </c>
       <c r="D154">
-        <v>-1.45721173286438</v>
+        <v>-0.2781022787094116</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -3585,7 +3585,7 @@
         <v>-9</v>
       </c>
       <c r="D155">
-        <v>-2.741718292236328</v>
+        <v>-2.08751106262207</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -3599,7 +3599,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D156">
-        <v>2.948948383331299</v>
+        <v>2.148908376693726</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -3613,7 +3613,7 @@
         <v>-3.599999904632568</v>
       </c>
       <c r="D157">
-        <v>-4.850967407226562</v>
+        <v>-1.594234585762024</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -3627,7 +3627,7 @@
         <v>-3.200000047683716</v>
       </c>
       <c r="D158">
-        <v>-16.46717643737793</v>
+        <v>-17.96776962280273</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -3641,7 +3641,7 @@
         <v>-30.79999923706055</v>
       </c>
       <c r="D159">
-        <v>-19.30027008056641</v>
+        <v>-20.81796264648438</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -3655,7 +3655,7 @@
         <v>-11.5</v>
       </c>
       <c r="D160">
-        <v>-7.701526165008545</v>
+        <v>-7.992609977722168</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -3669,7 +3669,7 @@
         <v>-21.60000038146973</v>
       </c>
       <c r="D161">
-        <v>-18.20937347412109</v>
+        <v>-20.27382469177246</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -3683,7 +3683,7 @@
         <v>-14.60000038146973</v>
       </c>
       <c r="D162">
-        <v>-10.42983341217041</v>
+        <v>-11.91588497161865</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -3697,7 +3697,7 @@
         <v>-2.5</v>
       </c>
       <c r="D163">
-        <v>-3.303402900695801</v>
+        <v>-4.133315086364746</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -3711,7 +3711,7 @@
         <v>2</v>
       </c>
       <c r="D164">
-        <v>2.51338005065918</v>
+        <v>3.635333299636841</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -3725,7 +3725,7 @@
         <v>-4.400000095367432</v>
       </c>
       <c r="D165">
-        <v>-1.498764514923096</v>
+        <v>-1.385682463645935</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -3739,7 +3739,7 @@
         <v>-12.39999961853027</v>
       </c>
       <c r="D166">
-        <v>-18.58669090270996</v>
+        <v>-20.92268371582031</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -3753,7 +3753,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D167">
-        <v>0.2377762794494629</v>
+        <v>-0.3663809299468994</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -3767,7 +3767,7 @@
         <v>-2</v>
       </c>
       <c r="D168">
-        <v>0.7253873348236084</v>
+        <v>0.3273095190525055</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -3781,7 +3781,7 @@
         <v>-6.699999809265137</v>
       </c>
       <c r="D169">
-        <v>-3.833354473114014</v>
+        <v>-7.041604042053223</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -3795,7 +3795,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D170">
-        <v>0.673105001449585</v>
+        <v>0.3813283741474152</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -3809,7 +3809,7 @@
         <v>-5</v>
       </c>
       <c r="D171">
-        <v>0.4575513601303101</v>
+        <v>0.08775904774665833</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -3823,7 +3823,7 @@
         <v>-1.299999952316284</v>
       </c>
       <c r="D172">
-        <v>-0.5355405807495117</v>
+        <v>-0.8023042678833008</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -3837,7 +3837,7 @@
         <v>-14.10000038146973</v>
       </c>
       <c r="D173">
-        <v>-9.080102920532227</v>
+        <v>-9.736534118652344</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -3851,7 +3851,7 @@
         <v>-6.599999904632568</v>
       </c>
       <c r="D174">
-        <v>-8.399524688720703</v>
+        <v>-9.045260429382324</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -3865,7 +3865,7 @@
         <v>9.399999618530273</v>
       </c>
       <c r="D175">
-        <v>10.33681678771973</v>
+        <v>9.342487335205078</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -3879,7 +3879,7 @@
         <v>-18.5</v>
       </c>
       <c r="D176">
-        <v>-17.2132568359375</v>
+        <v>-19.11656761169434</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -3893,7 +3893,7 @@
         <v>-16.20000076293945</v>
       </c>
       <c r="D177">
-        <v>-10.80657291412354</v>
+        <v>-12.28748798370361</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -3907,7 +3907,7 @@
         <v>0</v>
       </c>
       <c r="D178">
-        <v>-2.501566410064697</v>
+        <v>-2.069104671478271</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -3921,7 +3921,7 @@
         <v>25.29999923706055</v>
       </c>
       <c r="D179">
-        <v>15.38168716430664</v>
+        <v>13.13942909240723</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -3935,7 +3935,7 @@
         <v>-5.900000095367432</v>
       </c>
       <c r="D180">
-        <v>-8.21953010559082</v>
+        <v>-9.679858207702637</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -3949,7 +3949,7 @@
         <v>-7.300000190734863</v>
       </c>
       <c r="D181">
-        <v>-7.361432075500488</v>
+        <v>-7.457919120788574</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -3963,7 +3963,7 @@
         <v>-7.300000190734863</v>
       </c>
       <c r="D182">
-        <v>-5.549888610839844</v>
+        <v>-6.715565204620361</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -3977,7 +3977,7 @@
         <v>-24</v>
       </c>
       <c r="D183">
-        <v>-11.86844825744629</v>
+        <v>-10.83045768737793</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -3991,7 +3991,7 @@
         <v>-9</v>
       </c>
       <c r="D184">
-        <v>-0.4942042827606201</v>
+        <v>-2.53447413444519</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4005,7 +4005,7 @@
         <v>7.199999809265137</v>
       </c>
       <c r="D185">
-        <v>0.2630088329315186</v>
+        <v>-0.627406895160675</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4019,7 +4019,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D186">
-        <v>3.85538387298584</v>
+        <v>4.780439853668213</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4033,7 +4033,7 @@
         <v>-5</v>
       </c>
       <c r="D187">
-        <v>-4.489131450653076</v>
+        <v>-4.738787651062012</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4047,7 +4047,7 @@
         <v>-10.69999980926514</v>
       </c>
       <c r="D188">
-        <v>-3.673847675323486</v>
+        <v>-11.86578845977783</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4061,7 +4061,7 @@
         <v>-23.79999923706055</v>
       </c>
       <c r="D189">
-        <v>-15.24656295776367</v>
+        <v>-14.28679180145264</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4075,7 +4075,7 @@
         <v>-2</v>
       </c>
       <c r="D190">
-        <v>1.070160269737244</v>
+        <v>0.6775703430175781</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4089,7 +4089,7 @@
         <v>0.5</v>
       </c>
       <c r="D191">
-        <v>-0.3637402057647705</v>
+        <v>-0.6679868698120117</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4103,7 +4103,7 @@
         <v>-38.79999923706055</v>
       </c>
       <c r="D192">
-        <v>-23.75162124633789</v>
+        <v>-25.71994209289551</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4117,7 +4117,7 @@
         <v>-17.70000076293945</v>
       </c>
       <c r="D193">
-        <v>-17.06073379516602</v>
+        <v>-18.56549072265625</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4131,7 +4131,7 @@
         <v>13.30000019073486</v>
       </c>
       <c r="D194">
-        <v>3.948735237121582</v>
+        <v>4.544011116027832</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4145,7 +4145,7 @@
         <v>-18.39999961853027</v>
       </c>
       <c r="D195">
-        <v>-16.87224197387695</v>
+        <v>-19.94492721557617</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4159,7 +4159,7 @@
         <v>9.899999618530273</v>
       </c>
       <c r="D196">
-        <v>4.515429496765137</v>
+        <v>4.236639022827148</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4173,7 +4173,7 @@
         <v>-1.600000023841858</v>
       </c>
       <c r="D197">
-        <v>0.6197258234024048</v>
+        <v>0.5945491790771484</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4187,7 +4187,7 @@
         <v>-2</v>
       </c>
       <c r="D198">
-        <v>-0.4116008579730988</v>
+        <v>-0.7137409448623657</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4201,7 +4201,7 @@
         <v>-13.5</v>
       </c>
       <c r="D199">
-        <v>-5.147612571716309</v>
+        <v>-3.775937080383301</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4215,7 +4215,7 @@
         <v>-16.39999961853027</v>
       </c>
       <c r="D200">
-        <v>-9.180696487426758</v>
+        <v>-10.68365573883057</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4229,7 +4229,7 @@
         <v>-11.10000038146973</v>
       </c>
       <c r="D201">
-        <v>-10.10361480712891</v>
+        <v>-12.15373516082764</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4243,7 +4243,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D202">
-        <v>-3.155641078948975</v>
+        <v>-2.595367670059204</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4257,7 +4257,7 @@
         <v>4</v>
       </c>
       <c r="D203">
-        <v>1.667815804481506</v>
+        <v>0.875429630279541</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4271,7 +4271,7 @@
         <v>-14.5</v>
       </c>
       <c r="D204">
-        <v>-8.32030200958252</v>
+        <v>-8.383744239807129</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4285,7 +4285,7 @@
         <v>-3.5</v>
       </c>
       <c r="D205">
-        <v>-3.002593040466309</v>
+        <v>-2.426733016967773</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4299,7 +4299,7 @@
         <v>-4.5</v>
       </c>
       <c r="D206">
-        <v>-3.680928230285645</v>
+        <v>-3.718143939971924</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4313,7 +4313,7 @@
         <v>-5</v>
       </c>
       <c r="D207">
-        <v>-7.894836902618408</v>
+        <v>-9.36968994140625</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4327,7 +4327,7 @@
         <v>16.29999923706055</v>
       </c>
       <c r="D208">
-        <v>11.2457275390625</v>
+        <v>12.92597103118896</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4341,7 +4341,7 @@
         <v>-19.79999923706055</v>
       </c>
       <c r="D209">
-        <v>-19.46622848510742</v>
+        <v>-20.81489562988281</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4355,7 +4355,7 @@
         <v>-3.299999952316284</v>
       </c>
       <c r="D210">
-        <v>-2.932217597961426</v>
+        <v>-0.9717358350753784</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4369,7 +4369,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D211">
-        <v>0.3076885938644409</v>
+        <v>0.2855925858020782</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4383,7 +4383,7 @@
         <v>23.39999961853027</v>
       </c>
       <c r="D212">
-        <v>-9.859427452087402</v>
+        <v>-10.99922847747803</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4397,7 +4397,7 @@
         <v>-4.5</v>
       </c>
       <c r="D213">
-        <v>-1.989537239074707</v>
+        <v>-2.021209239959717</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4411,7 +4411,7 @@
         <v>-2.200000047683716</v>
       </c>
       <c r="D214">
-        <v>0.4499613046646118</v>
+        <v>0.3855220377445221</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4425,7 +4425,7 @@
         <v>-8.699999809265137</v>
       </c>
       <c r="D215">
-        <v>-6.041733741760254</v>
+        <v>-8.641934394836426</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4439,7 +4439,7 @@
         <v>-7.800000190734863</v>
       </c>
       <c r="D216">
-        <v>-6.74396800994873</v>
+        <v>-7.310356616973877</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4453,7 +4453,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D217">
-        <v>2.510185241699219</v>
+        <v>1.613380908966064</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4467,7 +4467,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D218">
-        <v>-0.3527194857597351</v>
+        <v>-0.2095185816287994</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4481,7 +4481,7 @@
         <v>4.199999809265137</v>
       </c>
       <c r="D219">
-        <v>3.262173652648926</v>
+        <v>1.783521413803101</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4495,7 +4495,7 @@
         <v>-9</v>
       </c>
       <c r="D220">
-        <v>-7.839936256408691</v>
+        <v>-9.119263648986816</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4509,7 +4509,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D221">
-        <v>-1.080889225006104</v>
+        <v>0.07493105530738831</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4523,7 +4523,7 @@
         <v>-34.70000076293945</v>
       </c>
       <c r="D222">
-        <v>-6.914444446563721</v>
+        <v>-8.296092987060547</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4537,7 +4537,7 @@
         <v>-11.19999980926514</v>
       </c>
       <c r="D223">
-        <v>-4.23698616027832</v>
+        <v>-4.552190780639648</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4551,7 +4551,7 @@
         <v>-17.10000038146973</v>
       </c>
       <c r="D224">
-        <v>-10.95201206207275</v>
+        <v>-11.81324672698975</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4565,7 +4565,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D225">
-        <v>3.221584320068359</v>
+        <v>3.250865936279297</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -4579,7 +4579,7 @@
         <v>5.900000095367432</v>
       </c>
       <c r="D226">
-        <v>3.081896781921387</v>
+        <v>3.598170518875122</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -4593,7 +4593,7 @@
         <v>-2.799999952316284</v>
       </c>
       <c r="D227">
-        <v>5.315966606140137</v>
+        <v>3.883789777755737</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -4607,7 +4607,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D228">
-        <v>0.6672519445419312</v>
+        <v>0.3296875059604645</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -4621,7 +4621,7 @@
         <v>-8</v>
       </c>
       <c r="D229">
-        <v>-1.814178943634033</v>
+        <v>-2.985871076583862</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -4635,7 +4635,7 @@
         <v>-1.5</v>
       </c>
       <c r="D230">
-        <v>1.373745560646057</v>
+        <v>-0.1433660686016083</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -4649,7 +4649,7 @@
         <v>-1.399999976158142</v>
       </c>
       <c r="D231">
-        <v>0.9943782091140747</v>
+        <v>0.2729423344135284</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -4663,7 +4663,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D232">
-        <v>1.050659775733948</v>
+        <v>1.091109275817871</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -4677,7 +4677,7 @@
         <v>8.899999618530273</v>
       </c>
       <c r="D233">
-        <v>3.410404205322266</v>
+        <v>1.860902547836304</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -4691,7 +4691,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D234">
-        <v>4.696455001831055</v>
+        <v>4.759454727172852</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -4705,7 +4705,7 @@
         <v>22.20000076293945</v>
       </c>
       <c r="D235">
-        <v>16.68951797485352</v>
+        <v>16.33897399902344</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -4719,7 +4719,7 @@
         <v>-6.400000095367432</v>
       </c>
       <c r="D236">
-        <v>-6.100221633911133</v>
+        <v>-5.74330997467041</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -4733,7 +4733,7 @@
         <v>-14.39999961853027</v>
       </c>
       <c r="D237">
-        <v>-8.36765193939209</v>
+        <v>-8.497096061706543</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -4747,7 +4747,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D238">
-        <v>0.6970034837722778</v>
+        <v>0.4070791304111481</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -4761,7 +4761,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D239">
-        <v>0.4432481527328491</v>
+        <v>-0.06225124001502991</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -4775,7 +4775,7 @@
         <v>-0.8999999761581421</v>
       </c>
       <c r="D240">
-        <v>-0.6751325130462646</v>
+        <v>-0.4894722402095795</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -4789,7 +4789,7 @@
         <v>-1.100000023841858</v>
       </c>
       <c r="D241">
-        <v>-1.853777050971985</v>
+        <v>-1.646142244338989</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -4803,7 +4803,7 @@
         <v>-11.89999961853027</v>
       </c>
       <c r="D242">
-        <v>-5.737640380859375</v>
+        <v>-5.353371143341064</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -4817,7 +4817,7 @@
         <v>-11.19999980926514</v>
       </c>
       <c r="D243">
-        <v>-6.494210720062256</v>
+        <v>-6.403522968292236</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -4831,7 +4831,7 @@
         <v>-2.799999952316284</v>
       </c>
       <c r="D244">
-        <v>1.716518998146057</v>
+        <v>0.9108327627182007</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -4845,7 +4845,7 @@
         <v>-7.800000190734863</v>
       </c>
       <c r="D245">
-        <v>-3.836637496948242</v>
+        <v>-4.963744640350342</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -4859,7 +4859,7 @@
         <v>-7.099999904632568</v>
       </c>
       <c r="D246">
-        <v>-3.813035011291504</v>
+        <v>-7.825561046600342</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -4873,7 +4873,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D247">
-        <v>-1.110034465789795</v>
+        <v>-0.9147523641586304</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -4887,7 +4887,7 @@
         <v>-8.800000190734863</v>
       </c>
       <c r="D248">
-        <v>-6.178131103515625</v>
+        <v>-6.731659889221191</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -4901,7 +4901,7 @@
         <v>-6.300000190734863</v>
       </c>
       <c r="D249">
-        <v>-0.4638111591339111</v>
+        <v>-0.4074452221393585</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -4915,7 +4915,7 @@
         <v>-2.900000095367432</v>
       </c>
       <c r="D250">
-        <v>-4.030190467834473</v>
+        <v>-3.944309949874878</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -4929,7 +4929,7 @@
         <v>-7.5</v>
       </c>
       <c r="D251">
-        <v>-4.39713191986084</v>
+        <v>-1.176095366477966</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -4943,7 +4943,7 @@
         <v>-20.89999961853027</v>
       </c>
       <c r="D252">
-        <v>-12.11618423461914</v>
+        <v>-12.68949699401855</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -4957,7 +4957,7 @@
         <v>-15.60000038146973</v>
       </c>
       <c r="D253">
-        <v>-12.93581390380859</v>
+        <v>-16.77822113037109</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -4971,7 +4971,7 @@
         <v>-0.8999999761581421</v>
       </c>
       <c r="D254">
-        <v>-8.136483192443848</v>
+        <v>-4.542327880859375</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -4985,7 +4985,7 @@
         <v>5.300000190734863</v>
       </c>
       <c r="D255">
-        <v>1.362573504447937</v>
+        <v>0.6721971035003662</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -4999,7 +4999,7 @@
         <v>-0.6000000238418579</v>
       </c>
       <c r="D256">
-        <v>-0.4731317162513733</v>
+        <v>1.279457569122314</v>
       </c>
     </row>
     <row r="257" spans="1:4">
@@ -5013,7 +5013,7 @@
         <v>-8.300000190734863</v>
       </c>
       <c r="D257">
-        <v>-6.117087364196777</v>
+        <v>-6.479853630065918</v>
       </c>
     </row>
     <row r="258" spans="1:4">
@@ -5027,7 +5027,7 @@
         <v>-12.39999961853027</v>
       </c>
       <c r="D258">
-        <v>-9.028200149536133</v>
+        <v>-8.857648849487305</v>
       </c>
     </row>
     <row r="259" spans="1:4">
@@ -5041,7 +5041,7 @@
         <v>-9.800000190734863</v>
       </c>
       <c r="D259">
-        <v>-7.583388328552246</v>
+        <v>-8.261946678161621</v>
       </c>
     </row>
     <row r="260" spans="1:4">
@@ -5055,7 +5055,7 @@
         <v>-10.5</v>
       </c>
       <c r="D260">
-        <v>-3.412295818328857</v>
+        <v>-2.567809343338013</v>
       </c>
     </row>
     <row r="261" spans="1:4">
@@ -5069,7 +5069,7 @@
         <v>6.800000190734863</v>
       </c>
       <c r="D261">
-        <v>2.818592071533203</v>
+        <v>1.683900594711304</v>
       </c>
     </row>
     <row r="262" spans="1:4">
@@ -5083,7 +5083,7 @@
         <v>-5.199999809265137</v>
       </c>
       <c r="D262">
-        <v>-4.476110935211182</v>
+        <v>-4.865490436553955</v>
       </c>
     </row>
     <row r="263" spans="1:4">
@@ -5097,7 +5097,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D263">
-        <v>0.8590916395187378</v>
+        <v>0.5420190095901489</v>
       </c>
     </row>
     <row r="264" spans="1:4">
@@ -5111,7 +5111,7 @@
         <v>-5</v>
       </c>
       <c r="D264">
-        <v>-2.052865505218506</v>
+        <v>-2.161532878875732</v>
       </c>
     </row>
     <row r="265" spans="1:4">
@@ -5125,7 +5125,7 @@
         <v>15.5</v>
       </c>
       <c r="D265">
-        <v>7.744387626647949</v>
+        <v>7.040339469909668</v>
       </c>
     </row>
     <row r="266" spans="1:4">
@@ -5139,7 +5139,7 @@
         <v>-1.399999976158142</v>
       </c>
       <c r="D266">
-        <v>-0.2729153037071228</v>
+        <v>-0.4466128647327423</v>
       </c>
     </row>
     <row r="267" spans="1:4">
@@ -5153,7 +5153,7 @@
         <v>-4.800000190734863</v>
       </c>
       <c r="D267">
-        <v>-0.8675854802131653</v>
+        <v>-0.1771561801433563</v>
       </c>
     </row>
     <row r="268" spans="1:4">
@@ -5167,7 +5167,7 @@
         <v>-3.200000047683716</v>
       </c>
       <c r="D268">
-        <v>-0.8814137578010559</v>
+        <v>-0.02730908989906311</v>
       </c>
     </row>
     <row r="269" spans="1:4">
@@ -5181,7 +5181,7 @@
         <v>18.89999961853027</v>
       </c>
       <c r="D269">
-        <v>9.709556579589844</v>
+        <v>9.384758949279785</v>
       </c>
     </row>
     <row r="270" spans="1:4">
@@ -5195,7 +5195,7 @@
         <v>-8.600000381469727</v>
       </c>
       <c r="D270">
-        <v>-5.07403564453125</v>
+        <v>-5.548631191253662</v>
       </c>
     </row>
     <row r="271" spans="1:4">
@@ -5209,7 +5209,7 @@
         <v>-1.799999952316284</v>
       </c>
       <c r="D271">
-        <v>-1.63474702835083</v>
+        <v>-0.9103713035583496</v>
       </c>
     </row>
     <row r="272" spans="1:4">
@@ -5223,7 +5223,7 @@
         <v>-18.20000076293945</v>
       </c>
       <c r="D272">
-        <v>-19.18507385253906</v>
+        <v>-18.88751792907715</v>
       </c>
     </row>
     <row r="273" spans="1:4">
@@ -5237,7 +5237,7 @@
         <v>-20.79999923706055</v>
       </c>
       <c r="D273">
-        <v>-14.36780452728271</v>
+        <v>-17.56670761108398</v>
       </c>
     </row>
     <row r="274" spans="1:4">
@@ -5251,7 +5251,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D274">
-        <v>1.533826947212219</v>
+        <v>1.017672061920166</v>
       </c>
     </row>
     <row r="275" spans="1:4">
@@ -5265,7 +5265,7 @@
         <v>-3.599999904632568</v>
       </c>
       <c r="D275">
-        <v>-2.895722389221191</v>
+        <v>-3.113390445709229</v>
       </c>
     </row>
     <row r="276" spans="1:4">
@@ -5279,7 +5279,7 @@
         <v>9.300000190734863</v>
       </c>
       <c r="D276">
-        <v>2.452888011932373</v>
+        <v>1.894521236419678</v>
       </c>
     </row>
     <row r="277" spans="1:4">
@@ -5293,7 +5293,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D277">
-        <v>-0.7430724501609802</v>
+        <v>0.5351667404174805</v>
       </c>
     </row>
     <row r="278" spans="1:4">
@@ -5307,7 +5307,7 @@
         <v>-15</v>
       </c>
       <c r="D278">
-        <v>-9.332282066345215</v>
+        <v>-11.44900798797607</v>
       </c>
     </row>
     <row r="279" spans="1:4">
@@ -5321,7 +5321,7 @@
         <v>-6.199999809265137</v>
       </c>
       <c r="D279">
-        <v>-5.23651123046875</v>
+        <v>-6.316681861877441</v>
       </c>
     </row>
     <row r="280" spans="1:4">
@@ -5335,7 +5335,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D280">
-        <v>1.242610454559326</v>
+        <v>1.604015588760376</v>
       </c>
     </row>
     <row r="281" spans="1:4">
@@ -5349,7 +5349,7 @@
         <v>-0.6000000238418579</v>
       </c>
       <c r="D281">
-        <v>-4.370236396789551</v>
+        <v>-6.270702362060547</v>
       </c>
     </row>
     <row r="282" spans="1:4">
@@ -5363,7 +5363,7 @@
         <v>15.69999980926514</v>
       </c>
       <c r="D282">
-        <v>2.518094539642334</v>
+        <v>2.072236299514771</v>
       </c>
     </row>
     <row r="283" spans="1:4">
@@ -5377,7 +5377,7 @@
         <v>-3</v>
       </c>
       <c r="D283">
-        <v>-2.948190689086914</v>
+        <v>-2.348027944564819</v>
       </c>
     </row>
     <row r="284" spans="1:4">
@@ -5391,7 +5391,7 @@
         <v>0</v>
       </c>
       <c r="D284">
-        <v>1.093334913253784</v>
+        <v>1.573585748672485</v>
       </c>
     </row>
     <row r="285" spans="1:4">
@@ -5405,7 +5405,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D285">
-        <v>0.9530576467514038</v>
+        <v>0.2156859934329987</v>
       </c>
     </row>
     <row r="286" spans="1:4">
@@ -5419,7 +5419,7 @@
         <v>-10.89999961853027</v>
       </c>
       <c r="D286">
-        <v>-8.560141563415527</v>
+        <v>-9.237833976745605</v>
       </c>
     </row>
     <row r="287" spans="1:4">
@@ -5433,7 +5433,7 @@
         <v>2</v>
       </c>
       <c r="D287">
-        <v>0.8112150430679321</v>
+        <v>0.04816964268684387</v>
       </c>
     </row>
     <row r="288" spans="1:4">
@@ -5447,7 +5447,7 @@
         <v>-1.899999976158142</v>
       </c>
       <c r="D288">
-        <v>1.332942128181458</v>
+        <v>-1.20541775226593</v>
       </c>
     </row>
     <row r="289" spans="1:4">
@@ -5461,7 +5461,7 @@
         <v>8</v>
       </c>
       <c r="D289">
-        <v>3.200370311737061</v>
+        <v>3.903632879257202</v>
       </c>
     </row>
     <row r="290" spans="1:4">
@@ -5475,7 +5475,7 @@
         <v>-11.30000019073486</v>
       </c>
       <c r="D290">
-        <v>-9.27557373046875</v>
+        <v>-10.05851078033447</v>
       </c>
     </row>
     <row r="291" spans="1:4">
@@ -5489,7 +5489,7 @@
         <v>-2.700000047683716</v>
       </c>
       <c r="D291">
-        <v>1.381066083908081</v>
+        <v>0.736083984375</v>
       </c>
     </row>
     <row r="292" spans="1:4">
@@ -5503,7 +5503,7 @@
         <v>-9.899999618530273</v>
       </c>
       <c r="D292">
-        <v>-7.075928688049316</v>
+        <v>-5.373240947723389</v>
       </c>
     </row>
     <row r="293" spans="1:4">
@@ -5517,7 +5517,7 @@
         <v>-7.5</v>
       </c>
       <c r="D293">
-        <v>-2.489733695983887</v>
+        <v>-4.13176155090332</v>
       </c>
     </row>
     <row r="294" spans="1:4">
@@ -5531,7 +5531,7 @@
         <v>-4.900000095367432</v>
       </c>
       <c r="D294">
-        <v>-11.10040664672852</v>
+        <v>-12.52628993988037</v>
       </c>
     </row>
     <row r="295" spans="1:4">
@@ -5545,7 +5545,7 @@
         <v>-4.900000095367432</v>
       </c>
       <c r="D295">
-        <v>-3.246119499206543</v>
+        <v>-2.779773712158203</v>
       </c>
     </row>
     <row r="296" spans="1:4">
@@ -5559,7 +5559,7 @@
         <v>-4.599999904632568</v>
       </c>
       <c r="D296">
-        <v>0.5728000402450562</v>
+        <v>0.08274087309837341</v>
       </c>
     </row>
     <row r="297" spans="1:4">
@@ -5573,7 +5573,7 @@
         <v>-7.199999809265137</v>
       </c>
       <c r="D297">
-        <v>-4.096538066864014</v>
+        <v>-5.260860919952393</v>
       </c>
     </row>
     <row r="298" spans="1:4">
@@ -5587,7 +5587,7 @@
         <v>-15.60000038146973</v>
       </c>
       <c r="D298">
-        <v>-11.89515113830566</v>
+        <v>-14.29540634155273</v>
       </c>
     </row>
     <row r="299" spans="1:4">
@@ -5601,7 +5601,7 @@
         <v>-0.6000000238418579</v>
       </c>
       <c r="D299">
-        <v>-5.487972736358643</v>
+        <v>-7.982929229736328</v>
       </c>
     </row>
     <row r="300" spans="1:4">
@@ -5615,7 +5615,7 @@
         <v>-11.5</v>
       </c>
       <c r="D300">
-        <v>-8.885826110839844</v>
+        <v>-8.294571876525879</v>
       </c>
     </row>
     <row r="301" spans="1:4">
@@ -5629,7 +5629,7 @@
         <v>-1.799999952316284</v>
       </c>
       <c r="D301">
-        <v>-1.010010004043579</v>
+        <v>-1.242080807685852</v>
       </c>
     </row>
     <row r="302" spans="1:4">
@@ -5643,7 +5643,7 @@
         <v>-12.60000038146973</v>
       </c>
       <c r="D302">
-        <v>-6.304805755615234</v>
+        <v>-7.543042182922363</v>
       </c>
     </row>
     <row r="303" spans="1:4">
@@ -5657,7 +5657,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D303">
-        <v>-0.06084975600242615</v>
+        <v>-0.1932747662067413</v>
       </c>
     </row>
     <row r="304" spans="1:4">
@@ -5671,7 +5671,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D304">
-        <v>0.4206793308258057</v>
+        <v>0.7402759790420532</v>
       </c>
     </row>
     <row r="305" spans="1:4">
@@ -5685,7 +5685,7 @@
         <v>-11.69999980926514</v>
       </c>
       <c r="D305">
-        <v>-8.995149612426758</v>
+        <v>-10.72500705718994</v>
       </c>
     </row>
     <row r="306" spans="1:4">
@@ -5699,7 +5699,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D306">
-        <v>-2.124611854553223</v>
+        <v>-1.571227073669434</v>
       </c>
     </row>
     <row r="307" spans="1:4">
@@ -5713,7 +5713,7 @@
         <v>5.5</v>
       </c>
       <c r="D307">
-        <v>2.550419807434082</v>
+        <v>0.9168709516525269</v>
       </c>
     </row>
     <row r="308" spans="1:4">
@@ -5727,7 +5727,7 @@
         <v>-5.5</v>
       </c>
       <c r="D308">
-        <v>-4.655791282653809</v>
+        <v>-4.350427627563477</v>
       </c>
     </row>
     <row r="309" spans="1:4">
@@ -5741,7 +5741,7 @@
         <v>-0.300000011920929</v>
       </c>
       <c r="D309">
-        <v>1.484532952308655</v>
+        <v>1.814375638961792</v>
       </c>
     </row>
     <row r="310" spans="1:4">
@@ -5755,7 +5755,7 @@
         <v>-2.400000095367432</v>
       </c>
       <c r="D310">
-        <v>-4.889957904815674</v>
+        <v>-5.141463279724121</v>
       </c>
     </row>
     <row r="311" spans="1:4">
@@ -5769,7 +5769,7 @@
         <v>-4.199999809265137</v>
       </c>
       <c r="D311">
-        <v>-6.207664489746094</v>
+        <v>-9.241292953491211</v>
       </c>
     </row>
     <row r="312" spans="1:4">
@@ -5783,7 +5783,7 @@
         <v>-1.299999952316284</v>
       </c>
       <c r="D312">
-        <v>-2.141017913818359</v>
+        <v>-3.16424822807312</v>
       </c>
     </row>
     <row r="313" spans="1:4">
@@ -5797,7 +5797,7 @@
         <v>11.5</v>
       </c>
       <c r="D313">
-        <v>3.554940700531006</v>
+        <v>2.486732959747314</v>
       </c>
     </row>
     <row r="314" spans="1:4">
@@ -5811,7 +5811,7 @@
         <v>4.099999904632568</v>
       </c>
       <c r="D314">
-        <v>2.877779006958008</v>
+        <v>3.067732095718384</v>
       </c>
     </row>
     <row r="315" spans="1:4">
@@ -5825,7 +5825,7 @@
         <v>9.399999618530273</v>
       </c>
       <c r="D315">
-        <v>2.200995922088623</v>
+        <v>0.8274109363555908</v>
       </c>
     </row>
     <row r="316" spans="1:4">
@@ -5839,7 +5839,7 @@
         <v>-4.099999904632568</v>
       </c>
       <c r="D316">
-        <v>-5.181076049804688</v>
+        <v>-5.880757808685303</v>
       </c>
     </row>
     <row r="317" spans="1:4">
@@ -5853,7 +5853,7 @@
         <v>4.199999809265137</v>
       </c>
       <c r="D317">
-        <v>0.8152395486831665</v>
+        <v>0.7941359281539917</v>
       </c>
     </row>
     <row r="318" spans="1:4">
@@ -5867,7 +5867,7 @@
         <v>-7.800000190734863</v>
       </c>
       <c r="D318">
-        <v>-6.852005958557129</v>
+        <v>-7.640888214111328</v>
       </c>
     </row>
     <row r="319" spans="1:4">
@@ -5881,7 +5881,7 @@
         <v>-0.300000011920929</v>
       </c>
       <c r="D319">
-        <v>-1.150241494178772</v>
+        <v>-1.028911471366882</v>
       </c>
     </row>
     <row r="320" spans="1:4">
@@ -5895,7 +5895,7 @@
         <v>13.30000019073486</v>
       </c>
       <c r="D320">
-        <v>8.735006332397461</v>
+        <v>9.380776405334473</v>
       </c>
     </row>
     <row r="321" spans="1:4">
@@ -5909,7 +5909,7 @@
         <v>-0.6000000238418579</v>
       </c>
       <c r="D321">
-        <v>-2.838358879089355</v>
+        <v>-4.222517967224121</v>
       </c>
     </row>
     <row r="322" spans="1:4">
@@ -5923,7 +5923,7 @@
         <v>-0.1000000014901161</v>
       </c>
       <c r="D322">
-        <v>5.753085136413574</v>
+        <v>4.225083351135254</v>
       </c>
     </row>
     <row r="323" spans="1:4">
@@ -5937,7 +5937,7 @@
         <v>-20.39999961853027</v>
       </c>
       <c r="D323">
-        <v>-17.89432525634766</v>
+        <v>-19.99202346801758</v>
       </c>
     </row>
     <row r="324" spans="1:4">
@@ -5951,7 +5951,7 @@
         <v>12.69999980926514</v>
       </c>
       <c r="D324">
-        <v>9.828893661499023</v>
+        <v>7.974697113037109</v>
       </c>
     </row>
     <row r="325" spans="1:4">
@@ -5965,7 +5965,7 @@
         <v>-22.39999961853027</v>
       </c>
       <c r="D325">
-        <v>-16.56534957885742</v>
+        <v>-19.2778377532959</v>
       </c>
     </row>
     <row r="326" spans="1:4">
@@ -5979,7 +5979,7 @@
         <v>-7.800000190734863</v>
       </c>
       <c r="D326">
-        <v>-0.007281243801116943</v>
+        <v>1.524495244026184</v>
       </c>
     </row>
     <row r="327" spans="1:4">
@@ -5993,7 +5993,7 @@
         <v>-5.400000095367432</v>
       </c>
       <c r="D327">
-        <v>-5.477855205535889</v>
+        <v>-7.494857311248779</v>
       </c>
     </row>
     <row r="328" spans="1:4">
@@ -6007,7 +6007,7 @@
         <v>17.29999923706055</v>
       </c>
       <c r="D328">
-        <v>2.129767894744873</v>
+        <v>1.29832661151886</v>
       </c>
     </row>
     <row r="329" spans="1:4">
@@ -6021,7 +6021,7 @@
         <v>21.5</v>
       </c>
       <c r="D329">
-        <v>9.256458282470703</v>
+        <v>10.17904567718506</v>
       </c>
     </row>
     <row r="330" spans="1:4">
@@ -6035,7 +6035,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D330">
-        <v>-0.04951485991477966</v>
+        <v>0.60638427734375</v>
       </c>
     </row>
     <row r="331" spans="1:4">
@@ -6049,7 +6049,7 @@
         <v>1</v>
       </c>
       <c r="D331">
-        <v>4.415603637695312</v>
+        <v>3.421575307846069</v>
       </c>
     </row>
     <row r="332" spans="1:4">
@@ -6063,7 +6063,7 @@
         <v>-16.60000038146973</v>
       </c>
       <c r="D332">
-        <v>-14.84257507324219</v>
+        <v>-15.83210849761963</v>
       </c>
     </row>
     <row r="333" spans="1:4">
@@ -6077,7 +6077,7 @@
         <v>-0.300000011920929</v>
       </c>
       <c r="D333">
-        <v>-2.076205253601074</v>
+        <v>-9.79598331451416</v>
       </c>
     </row>
     <row r="334" spans="1:4">
@@ -6091,7 +6091,7 @@
         <v>-1.399999976158142</v>
       </c>
       <c r="D334">
-        <v>0.498429536819458</v>
+        <v>-0.4194297194480896</v>
       </c>
     </row>
     <row r="335" spans="1:4">
@@ -6105,7 +6105,7 @@
         <v>-14.39999961853027</v>
       </c>
       <c r="D335">
-        <v>-6.950994968414307</v>
+        <v>-8.23646068572998</v>
       </c>
     </row>
     <row r="336" spans="1:4">
@@ -6119,7 +6119,7 @@
         <v>-12.5</v>
       </c>
       <c r="D336">
-        <v>-7.636792659759521</v>
+        <v>-8.820274353027344</v>
       </c>
     </row>
     <row r="337" spans="1:4">
@@ -6133,7 +6133,7 @@
         <v>-3.400000095367432</v>
       </c>
       <c r="D337">
-        <v>-5.712233066558838</v>
+        <v>-7.359312057495117</v>
       </c>
     </row>
     <row r="338" spans="1:4">
@@ -6147,7 +6147,7 @@
         <v>-10.60000038146973</v>
       </c>
       <c r="D338">
-        <v>-4.267639636993408</v>
+        <v>-5.59285831451416</v>
       </c>
     </row>
     <row r="339" spans="1:4">
@@ -6161,7 +6161,7 @@
         <v>-0.8999999761581421</v>
       </c>
       <c r="D339">
-        <v>0.01084399223327637</v>
+        <v>0.01150768995285034</v>
       </c>
     </row>
     <row r="340" spans="1:4">
@@ -6175,7 +6175,7 @@
         <v>-1</v>
       </c>
       <c r="D340">
-        <v>-0.870206356048584</v>
+        <v>-0.9775711297988892</v>
       </c>
     </row>
     <row r="341" spans="1:4">
@@ -6189,7 +6189,7 @@
         <v>-1.600000023841858</v>
       </c>
       <c r="D341">
-        <v>-1.562718987464905</v>
+        <v>-0.7279521226882935</v>
       </c>
     </row>
     <row r="342" spans="1:4">
@@ -6203,7 +6203,7 @@
         <v>-1.399999976158142</v>
       </c>
       <c r="D342">
-        <v>-0.1436697840690613</v>
+        <v>0.03407958149909973</v>
       </c>
     </row>
     <row r="343" spans="1:4">
@@ -6217,7 +6217,7 @@
         <v>-7.400000095367432</v>
       </c>
       <c r="D343">
-        <v>-3.466591835021973</v>
+        <v>-5.126076221466064</v>
       </c>
     </row>
     <row r="344" spans="1:4">
@@ -6231,7 +6231,7 @@
         <v>-14.10000038146973</v>
       </c>
       <c r="D344">
-        <v>-9.806130409240723</v>
+        <v>-10.46533012390137</v>
       </c>
     </row>
     <row r="345" spans="1:4">
@@ -6245,7 +6245,7 @@
         <v>-2.299999952316284</v>
       </c>
       <c r="D345">
-        <v>14.82536029815674</v>
+        <v>4.535824775695801</v>
       </c>
     </row>
     <row r="346" spans="1:4">
@@ -6259,7 +6259,7 @@
         <v>7</v>
       </c>
       <c r="D346">
-        <v>0.07932114601135254</v>
+        <v>-0.0982220470905304</v>
       </c>
     </row>
     <row r="347" spans="1:4">
@@ -6273,7 +6273,7 @@
         <v>-11.89999961853027</v>
       </c>
       <c r="D347">
-        <v>-11.14795303344727</v>
+        <v>-11.29429340362549</v>
       </c>
     </row>
     <row r="348" spans="1:4">
@@ -6287,7 +6287,7 @@
         <v>13.10000038146973</v>
       </c>
       <c r="D348">
-        <v>10.84475708007812</v>
+        <v>11.8358793258667</v>
       </c>
     </row>
     <row r="349" spans="1:4">
@@ -6301,7 +6301,7 @@
         <v>-3.299999952316284</v>
       </c>
       <c r="D349">
-        <v>0.8119391202926636</v>
+        <v>-0.4475567638874054</v>
       </c>
     </row>
     <row r="350" spans="1:4">
@@ -6315,7 +6315,7 @@
         <v>-2.599999904632568</v>
       </c>
       <c r="D350">
-        <v>-2.828273773193359</v>
+        <v>-1.310559272766113</v>
       </c>
     </row>
     <row r="351" spans="1:4">
@@ -6329,7 +6329,7 @@
         <v>-4</v>
       </c>
       <c r="D351">
-        <v>-1.359821081161499</v>
+        <v>-2.125432729721069</v>
       </c>
     </row>
     <row r="352" spans="1:4">
@@ -6343,7 +6343,7 @@
         <v>0</v>
       </c>
       <c r="D352">
-        <v>-15.15851974487305</v>
+        <v>-16.42227363586426</v>
       </c>
     </row>
     <row r="353" spans="1:4">
@@ -6357,7 +6357,7 @@
         <v>-2.299999952316284</v>
       </c>
       <c r="D353">
-        <v>-1.461031675338745</v>
+        <v>-3.434134006500244</v>
       </c>
     </row>
     <row r="354" spans="1:4">
@@ -6371,7 +6371,7 @@
         <v>-2.200000047683716</v>
       </c>
       <c r="D354">
-        <v>2.958601474761963</v>
+        <v>2.486341238021851</v>
       </c>
     </row>
     <row r="355" spans="1:4">
@@ -6385,7 +6385,7 @@
         <v>-14.19999980926514</v>
       </c>
       <c r="D355">
-        <v>-5.306877613067627</v>
+        <v>-8.268881797790527</v>
       </c>
     </row>
     <row r="356" spans="1:4">
@@ -6399,7 +6399,7 @@
         <v>8.199999809265137</v>
       </c>
       <c r="D356">
-        <v>4.624482154846191</v>
+        <v>4.869108200073242</v>
       </c>
     </row>
     <row r="357" spans="1:4">
@@ -6413,7 +6413,7 @@
         <v>-3.900000095367432</v>
       </c>
       <c r="D357">
-        <v>-1.032613515853882</v>
+        <v>-0.1128098666667938</v>
       </c>
     </row>
     <row r="358" spans="1:4">
@@ -6427,7 +6427,7 @@
         <v>-5.900000095367432</v>
       </c>
       <c r="D358">
-        <v>-3.385947227478027</v>
+        <v>-4.417736053466797</v>
       </c>
     </row>
     <row r="359" spans="1:4">
@@ -6441,7 +6441,7 @@
         <v>-11.30000019073486</v>
       </c>
       <c r="D359">
-        <v>-8.108078956604004</v>
+        <v>-9.412598609924316</v>
       </c>
     </row>
     <row r="360" spans="1:4">
@@ -6455,7 +6455,7 @@
         <v>0.5</v>
       </c>
       <c r="D360">
-        <v>1.149606108665466</v>
+        <v>1.026224374771118</v>
       </c>
     </row>
     <row r="361" spans="1:4">
@@ -6469,7 +6469,7 @@
         <v>-5.800000190734863</v>
       </c>
       <c r="D361">
-        <v>-7.963537216186523</v>
+        <v>-9.952567100524902</v>
       </c>
     </row>
     <row r="362" spans="1:4">
@@ -6483,7 +6483,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D362">
-        <v>-3.452133655548096</v>
+        <v>-4.551066398620605</v>
       </c>
     </row>
     <row r="363" spans="1:4">
@@ -6497,7 +6497,7 @@
         <v>-2.599999904632568</v>
       </c>
       <c r="D363">
-        <v>-0.08737412095069885</v>
+        <v>0.7692539691925049</v>
       </c>
     </row>
     <row r="364" spans="1:4">
@@ -6511,7 +6511,7 @@
         <v>-6.5</v>
       </c>
       <c r="D364">
-        <v>-1.563988447189331</v>
+        <v>-1.389580130577087</v>
       </c>
     </row>
     <row r="365" spans="1:4">
@@ -6525,7 +6525,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D365">
-        <v>3.259539127349854</v>
+        <v>2.685511350631714</v>
       </c>
     </row>
     <row r="366" spans="1:4">
@@ -6539,7 +6539,7 @@
         <v>-4.400000095367432</v>
       </c>
       <c r="D366">
-        <v>-0.7754977345466614</v>
+        <v>-0.6954980492591858</v>
       </c>
     </row>
     <row r="367" spans="1:4">
@@ -6553,7 +6553,7 @@
         <v>-11.39999961853027</v>
       </c>
       <c r="D367">
-        <v>-10.34789657592773</v>
+        <v>-11.53354740142822</v>
       </c>
     </row>
     <row r="368" spans="1:4">
@@ -6567,7 +6567,7 @@
         <v>-40.90000152587891</v>
       </c>
       <c r="D368">
-        <v>-30.35714340209961</v>
+        <v>-31.06300354003906</v>
       </c>
     </row>
     <row r="369" spans="1:4">
@@ -6581,7 +6581,7 @@
         <v>-5.900000095367432</v>
       </c>
       <c r="D369">
-        <v>-2.393621921539307</v>
+        <v>-2.919061183929443</v>
       </c>
     </row>
     <row r="370" spans="1:4">
@@ -6595,7 +6595,7 @@
         <v>-17.5</v>
       </c>
       <c r="D370">
-        <v>-13.84708499908447</v>
+        <v>-15.04742336273193</v>
       </c>
     </row>
     <row r="371" spans="1:4">
@@ -6609,7 +6609,7 @@
         <v>-2.799999952316284</v>
       </c>
       <c r="D371">
-        <v>-3.682498931884766</v>
+        <v>-4.459743022918701</v>
       </c>
     </row>
     <row r="372" spans="1:4">
@@ -6623,7 +6623,7 @@
         <v>-6.900000095367432</v>
       </c>
       <c r="D372">
-        <v>-4.562922477722168</v>
+        <v>-4.869650840759277</v>
       </c>
     </row>
     <row r="373" spans="1:4">
@@ -6637,7 +6637,7 @@
         <v>-1.600000023841858</v>
       </c>
       <c r="D373">
-        <v>-0.1138492822647095</v>
+        <v>-0.9312084913253784</v>
       </c>
     </row>
     <row r="374" spans="1:4">
@@ -6651,7 +6651,7 @@
         <v>-6.900000095367432</v>
       </c>
       <c r="D374">
-        <v>-4.476739406585693</v>
+        <v>-4.872025012969971</v>
       </c>
     </row>
     <row r="375" spans="1:4">
@@ -6665,7 +6665,7 @@
         <v>-20.39999961853027</v>
       </c>
       <c r="D375">
-        <v>-4.406761646270752</v>
+        <v>-2.425235033035278</v>
       </c>
     </row>
     <row r="376" spans="1:4">
@@ -6679,7 +6679,7 @@
         <v>0.5</v>
       </c>
       <c r="D376">
-        <v>1.733600974082947</v>
+        <v>2.329119920730591</v>
       </c>
     </row>
     <row r="377" spans="1:4">
@@ -6693,7 +6693,7 @@
         <v>-5.599999904632568</v>
       </c>
       <c r="D377">
-        <v>-4.479079723358154</v>
+        <v>-4.503071308135986</v>
       </c>
     </row>
     <row r="378" spans="1:4">
@@ -6707,7 +6707,7 @@
         <v>-7.099999904632568</v>
       </c>
       <c r="D378">
-        <v>-8.13966178894043</v>
+        <v>-7.249464988708496</v>
       </c>
     </row>
     <row r="379" spans="1:4">
@@ -6721,7 +6721,7 @@
         <v>-4.400000095367432</v>
       </c>
       <c r="D379">
-        <v>-1.051133990287781</v>
+        <v>-3.004553556442261</v>
       </c>
     </row>
     <row r="380" spans="1:4">
@@ -6735,7 +6735,7 @@
         <v>-7</v>
       </c>
       <c r="D380">
-        <v>-8.075640678405762</v>
+        <v>-8.600228309631348</v>
       </c>
     </row>
     <row r="381" spans="1:4">
@@ -6749,7 +6749,7 @@
         <v>-14.19999980926514</v>
       </c>
       <c r="D381">
-        <v>-6.599200248718262</v>
+        <v>-7.39874267578125</v>
       </c>
     </row>
     <row r="382" spans="1:4">
@@ -6763,7 +6763,7 @@
         <v>1.5</v>
       </c>
       <c r="D382">
-        <v>-0.6245025992393494</v>
+        <v>0.4310993254184723</v>
       </c>
     </row>
     <row r="383" spans="1:4">
@@ -6777,7 +6777,7 @@
         <v>-2.799999952316284</v>
       </c>
       <c r="D383">
-        <v>-0.09656110405921936</v>
+        <v>-0.670358419418335</v>
       </c>
     </row>
     <row r="384" spans="1:4">
@@ -6791,7 +6791,7 @@
         <v>-2</v>
       </c>
       <c r="D384">
-        <v>-2.393509149551392</v>
+        <v>-2.02450966835022</v>
       </c>
     </row>
     <row r="385" spans="1:4">
@@ -6805,7 +6805,7 @@
         <v>-8</v>
       </c>
       <c r="D385">
-        <v>-3.961673259735107</v>
+        <v>-3.355187654495239</v>
       </c>
     </row>
     <row r="386" spans="1:4">
@@ -6819,7 +6819,7 @@
         <v>-8.800000190734863</v>
       </c>
       <c r="D386">
-        <v>-2.608764171600342</v>
+        <v>-1.639832496643066</v>
       </c>
     </row>
     <row r="387" spans="1:4">
@@ -6833,7 +6833,7 @@
         <v>-11.5</v>
       </c>
       <c r="D387">
-        <v>-8.704774856567383</v>
+        <v>-9.554096221923828</v>
       </c>
     </row>
     <row r="388" spans="1:4">
@@ -6847,7 +6847,7 @@
         <v>-8.5</v>
       </c>
       <c r="D388">
-        <v>-8.831748008728027</v>
+        <v>-9.041346549987793</v>
       </c>
     </row>
     <row r="389" spans="1:4">
@@ -6861,7 +6861,7 @@
         <v>2.5</v>
       </c>
       <c r="D389">
-        <v>1.213962435722351</v>
+        <v>1.418869256973267</v>
       </c>
     </row>
     <row r="390" spans="1:4">
@@ -6875,7 +6875,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D390">
-        <v>-4.316367149353027</v>
+        <v>-0.7699089050292969</v>
       </c>
     </row>
     <row r="391" spans="1:4">
@@ -6889,7 +6889,7 @@
         <v>-9.800000190734863</v>
       </c>
       <c r="D391">
-        <v>-8.071030616760254</v>
+        <v>-9.444353103637695</v>
       </c>
     </row>
     <row r="392" spans="1:4">
@@ -6903,7 +6903,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D392">
-        <v>0.6451020240783691</v>
+        <v>-0.3570908904075623</v>
       </c>
     </row>
     <row r="393" spans="1:4">
@@ -6917,7 +6917,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D393">
-        <v>1.000285148620605</v>
+        <v>0.2246676981449127</v>
       </c>
     </row>
     <row r="394" spans="1:4">
@@ -6931,7 +6931,7 @@
         <v>-8.899999618530273</v>
       </c>
       <c r="D394">
-        <v>-2.055714845657349</v>
+        <v>-3.164002180099487</v>
       </c>
     </row>
     <row r="395" spans="1:4">
@@ -6945,7 +6945,7 @@
         <v>-38</v>
       </c>
       <c r="D395">
-        <v>-21.34706497192383</v>
+        <v>-27.97249984741211</v>
       </c>
     </row>
     <row r="396" spans="1:4">
@@ -6959,7 +6959,7 @@
         <v>-0.8999999761581421</v>
       </c>
       <c r="D396">
-        <v>-1.513603091239929</v>
+        <v>-3.099223375320435</v>
       </c>
     </row>
     <row r="397" spans="1:4">
@@ -6973,7 +6973,7 @@
         <v>-0.6000000238418579</v>
       </c>
       <c r="D397">
-        <v>-8.390701293945312</v>
+        <v>-8.787426948547363</v>
       </c>
     </row>
     <row r="398" spans="1:4">
@@ -6987,7 +6987,7 @@
         <v>-9.600000381469727</v>
       </c>
       <c r="D398">
-        <v>-5.196020603179932</v>
+        <v>-5.260627746582031</v>
       </c>
     </row>
     <row r="399" spans="1:4">
@@ -7001,7 +7001,7 @@
         <v>8.899999618530273</v>
       </c>
       <c r="D399">
-        <v>-3.356542587280273</v>
+        <v>-3.180739879608154</v>
       </c>
     </row>
     <row r="400" spans="1:4">
@@ -7015,7 +7015,7 @@
         <v>-10.10000038146973</v>
       </c>
       <c r="D400">
-        <v>-2.330099582672119</v>
+        <v>-3.926306962966919</v>
       </c>
     </row>
     <row r="401" spans="1:4">
@@ -7029,7 +7029,7 @@
         <v>0</v>
       </c>
       <c r="D401">
-        <v>0.1941144466400146</v>
+        <v>-0.6005895733833313</v>
       </c>
     </row>
     <row r="402" spans="1:4">
@@ -7043,7 +7043,7 @@
         <v>9.5</v>
       </c>
       <c r="D402">
-        <v>3.227225303649902</v>
+        <v>3.219729900360107</v>
       </c>
     </row>
     <row r="403" spans="1:4">
@@ -7057,7 +7057,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D403">
-        <v>3.169844627380371</v>
+        <v>3.597868680953979</v>
       </c>
     </row>
     <row r="404" spans="1:4">
@@ -7071,7 +7071,7 @@
         <v>9.600000381469727</v>
       </c>
       <c r="D404">
-        <v>1.229017615318298</v>
+        <v>-0.3184706270694733</v>
       </c>
     </row>
     <row r="405" spans="1:4">
@@ -7085,7 +7085,7 @@
         <v>-19.39999961853027</v>
       </c>
       <c r="D405">
-        <v>-19.08038330078125</v>
+        <v>-19.5093936920166</v>
       </c>
     </row>
     <row r="406" spans="1:4">
@@ -7099,7 +7099,7 @@
         <v>-11.5</v>
       </c>
       <c r="D406">
-        <v>-8.949414253234863</v>
+        <v>-10.03646373748779</v>
       </c>
     </row>
     <row r="407" spans="1:4">
@@ -7113,7 +7113,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D407">
-        <v>1.543341279029846</v>
+        <v>0.6371060609817505</v>
       </c>
     </row>
     <row r="408" spans="1:4">
@@ -7127,7 +7127,7 @@
         <v>-5.199999809265137</v>
       </c>
       <c r="D408">
-        <v>-2.304789066314697</v>
+        <v>-2.820738554000854</v>
       </c>
     </row>
     <row r="409" spans="1:4">
@@ -7141,7 +7141,7 @@
         <v>-5.699999809265137</v>
       </c>
       <c r="D409">
-        <v>-4.241425037384033</v>
+        <v>-4.419538974761963</v>
       </c>
     </row>
     <row r="410" spans="1:4">
@@ -7155,7 +7155,7 @@
         <v>-8.800000190734863</v>
       </c>
       <c r="D410">
-        <v>-7.794073104858398</v>
+        <v>-8.906613349914551</v>
       </c>
     </row>
     <row r="411" spans="1:4">
@@ -7169,7 +7169,7 @@
         <v>-10.80000019073486</v>
       </c>
       <c r="D411">
-        <v>-3.560285568237305</v>
+        <v>-5.929257869720459</v>
       </c>
     </row>
     <row r="412" spans="1:4">
@@ -7183,7 +7183,7 @@
         <v>-3.599999904632568</v>
       </c>
       <c r="D412">
-        <v>-7.88420295715332</v>
+        <v>-7.430018901824951</v>
       </c>
     </row>
     <row r="413" spans="1:4">
@@ -7197,7 +7197,7 @@
         <v>7.699999809265137</v>
       </c>
       <c r="D413">
-        <v>2.74237585067749</v>
+        <v>2.508258581161499</v>
       </c>
     </row>
     <row r="414" spans="1:4">
@@ -7211,7 +7211,7 @@
         <v>5.699999809265137</v>
       </c>
       <c r="D414">
-        <v>3.01075267791748</v>
+        <v>1.482342958450317</v>
       </c>
     </row>
     <row r="415" spans="1:4">
@@ -7225,7 +7225,7 @@
         <v>-4.199999809265137</v>
       </c>
       <c r="D415">
-        <v>-1.831434369087219</v>
+        <v>-1.77355170249939</v>
       </c>
     </row>
     <row r="416" spans="1:4">
@@ -7239,7 +7239,7 @@
         <v>-0.699999988079071</v>
       </c>
       <c r="D416">
-        <v>1.759807705879211</v>
+        <v>0.8821790218353271</v>
       </c>
     </row>
     <row r="417" spans="1:4">
@@ -7253,7 +7253,7 @@
         <v>-14.39999961853027</v>
       </c>
       <c r="D417">
-        <v>-4.568234443664551</v>
+        <v>-7.115278244018555</v>
       </c>
     </row>
     <row r="418" spans="1:4">
@@ -7267,7 +7267,7 @@
         <v>-20.70000076293945</v>
       </c>
       <c r="D418">
-        <v>-19.73503875732422</v>
+        <v>-20.23912620544434</v>
       </c>
     </row>
     <row r="419" spans="1:4">
@@ -7281,7 +7281,7 @@
         <v>-12.30000019073486</v>
       </c>
       <c r="D419">
-        <v>-0.9536494612693787</v>
+        <v>-0.2744234800338745</v>
       </c>
     </row>
     <row r="420" spans="1:4">
@@ -7295,7 +7295,7 @@
         <v>6.699999809265137</v>
       </c>
       <c r="D420">
-        <v>0.2935249805450439</v>
+        <v>0.9823678731918335</v>
       </c>
     </row>
     <row r="421" spans="1:4">
@@ -7309,7 +7309,7 @@
         <v>-9.600000381469727</v>
       </c>
       <c r="D421">
-        <v>-3.311708450317383</v>
+        <v>-4.347411155700684</v>
       </c>
     </row>
     <row r="422" spans="1:4">
@@ -7323,7 +7323,7 @@
         <v>-14.39999961853027</v>
       </c>
       <c r="D422">
-        <v>-8.382552146911621</v>
+        <v>-9.016788482666016</v>
       </c>
     </row>
     <row r="423" spans="1:4">
@@ -7337,7 +7337,7 @@
         <v>-2.900000095367432</v>
       </c>
       <c r="D423">
-        <v>-2.474928379058838</v>
+        <v>-3.721484184265137</v>
       </c>
     </row>
     <row r="424" spans="1:4">
@@ -7351,7 +7351,7 @@
         <v>-0.2000000029802322</v>
       </c>
       <c r="D424">
-        <v>0.323789119720459</v>
+        <v>0.4192937910556793</v>
       </c>
     </row>
     <row r="425" spans="1:4">
@@ -7365,7 +7365,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D425">
-        <v>0.8056801557540894</v>
+        <v>1.321352958679199</v>
       </c>
     </row>
     <row r="426" spans="1:4">
@@ -7379,7 +7379,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D426">
-        <v>-0.01420557498931885</v>
+        <v>-0.441243439912796</v>
       </c>
     </row>
     <row r="427" spans="1:4">
@@ -7393,7 +7393,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D427">
-        <v>-2.224812030792236</v>
+        <v>-1.453775644302368</v>
       </c>
     </row>
     <row r="428" spans="1:4">
@@ -7407,7 +7407,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D428">
-        <v>0.3945635557174683</v>
+        <v>1.791782379150391</v>
       </c>
     </row>
     <row r="429" spans="1:4">
@@ -7421,7 +7421,7 @@
         <v>-3.5</v>
       </c>
       <c r="D429">
-        <v>-4.325643539428711</v>
+        <v>-7.67948055267334</v>
       </c>
     </row>
     <row r="430" spans="1:4">
@@ -7435,7 +7435,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D430">
-        <v>0.08428847789764404</v>
+        <v>0.01653152704238892</v>
       </c>
     </row>
     <row r="431" spans="1:4">
@@ -7449,7 +7449,7 @@
         <v>-29.60000038146973</v>
       </c>
       <c r="D431">
-        <v>-20.85311889648438</v>
+        <v>-23.04870796203613</v>
       </c>
     </row>
     <row r="432" spans="1:4">
@@ -7463,7 +7463,7 @@
         <v>-7.400000095367432</v>
       </c>
       <c r="D432">
-        <v>-1.522259950637817</v>
+        <v>-3.791620492935181</v>
       </c>
     </row>
     <row r="433" spans="1:4">
@@ -7477,7 +7477,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D433">
-        <v>1.603755354881287</v>
+        <v>0.9911353588104248</v>
       </c>
     </row>
     <row r="434" spans="1:4">
@@ -7491,7 +7491,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D434">
-        <v>0.5064395666122437</v>
+        <v>-0.4543614983558655</v>
       </c>
     </row>
     <row r="435" spans="1:4">
@@ -7505,7 +7505,7 @@
         <v>-19.5</v>
       </c>
       <c r="D435">
-        <v>-19.01728248596191</v>
+        <v>-17.88375091552734</v>
       </c>
     </row>
     <row r="436" spans="1:4">
@@ -7519,7 +7519,7 @@
         <v>-0.300000011920929</v>
       </c>
       <c r="D436">
-        <v>0.6508747339248657</v>
+        <v>0.519895076751709</v>
       </c>
     </row>
     <row r="437" spans="1:4">
@@ -7533,7 +7533,7 @@
         <v>-3.400000095367432</v>
       </c>
       <c r="D437">
-        <v>0.7899664640426636</v>
+        <v>0.1054937541484833</v>
       </c>
     </row>
     <row r="438" spans="1:4">
@@ -7547,7 +7547,7 @@
         <v>-1.100000023841858</v>
       </c>
       <c r="D438">
-        <v>-1.63023853302002</v>
+        <v>-0.9717320203781128</v>
       </c>
     </row>
     <row r="439" spans="1:4">
@@ -7561,7 +7561,7 @@
         <v>-18.5</v>
       </c>
       <c r="D439">
-        <v>-3.417817115783691</v>
+        <v>1.037970304489136</v>
       </c>
     </row>
     <row r="440" spans="1:4">
@@ -7575,7 +7575,7 @@
         <v>-18</v>
       </c>
       <c r="D440">
-        <v>-15.56539726257324</v>
+        <v>-15.51083374023438</v>
       </c>
     </row>
     <row r="441" spans="1:4">
@@ -7589,7 +7589,7 @@
         <v>-8.5</v>
       </c>
       <c r="D441">
-        <v>-7.460791110992432</v>
+        <v>-8.722183227539062</v>
       </c>
     </row>
     <row r="442" spans="1:4">
@@ -7603,7 +7603,7 @@
         <v>-9</v>
       </c>
       <c r="D442">
-        <v>-5.624850749969482</v>
+        <v>-8.428369522094727</v>
       </c>
     </row>
     <row r="443" spans="1:4">
@@ -7617,7 +7617,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D443">
-        <v>1.683617234230042</v>
+        <v>1.563838481903076</v>
       </c>
     </row>
     <row r="444" spans="1:4">
@@ -7631,7 +7631,7 @@
         <v>4.099999904632568</v>
       </c>
       <c r="D444">
-        <v>2.434134960174561</v>
+        <v>1.435081720352173</v>
       </c>
     </row>
     <row r="445" spans="1:4">
@@ -7645,7 +7645,7 @@
         <v>-0.699999988079071</v>
       </c>
       <c r="D445">
-        <v>1.313031792640686</v>
+        <v>1.127833604812622</v>
       </c>
     </row>
     <row r="446" spans="1:4">
@@ -7659,7 +7659,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D446">
-        <v>0.5443698167800903</v>
+        <v>0.1924825012683868</v>
       </c>
     </row>
     <row r="447" spans="1:4">
@@ -7673,7 +7673,7 @@
         <v>5.300000190734863</v>
       </c>
       <c r="D447">
-        <v>-1.530109643936157</v>
+        <v>-1.324371933937073</v>
       </c>
     </row>
     <row r="448" spans="1:4">
@@ -7687,7 +7687,7 @@
         <v>-14.69999980926514</v>
       </c>
       <c r="D448">
-        <v>-10.23463153839111</v>
+        <v>-9.329963684082031</v>
       </c>
     </row>
     <row r="449" spans="1:4">
@@ -7701,7 +7701,7 @@
         <v>-8.899999618530273</v>
       </c>
       <c r="D449">
-        <v>-7.304917335510254</v>
+        <v>-6.119572162628174</v>
       </c>
     </row>
     <row r="450" spans="1:4">
@@ -7715,7 +7715,7 @@
         <v>-16.60000038146973</v>
       </c>
       <c r="D450">
-        <v>-14.14388465881348</v>
+        <v>-16.24572372436523</v>
       </c>
     </row>
     <row r="451" spans="1:4">
@@ -7729,7 +7729,7 @@
         <v>-5.800000190734863</v>
       </c>
       <c r="D451">
-        <v>-3.000543594360352</v>
+        <v>-5.222418308258057</v>
       </c>
     </row>
     <row r="452" spans="1:4">
@@ -7743,7 +7743,7 @@
         <v>9</v>
       </c>
       <c r="D452">
-        <v>5.020225524902344</v>
+        <v>4.222303867340088</v>
       </c>
     </row>
     <row r="453" spans="1:4">
@@ -7757,7 +7757,7 @@
         <v>-1.200000047683716</v>
       </c>
       <c r="D453">
-        <v>-0.50495445728302</v>
+        <v>-2.172802448272705</v>
       </c>
     </row>
     <row r="454" spans="1:4">
@@ -7771,7 +7771,7 @@
         <v>-4.699999809265137</v>
       </c>
       <c r="D454">
-        <v>4.091181755065918</v>
+        <v>3.168861627578735</v>
       </c>
     </row>
     <row r="455" spans="1:4">
@@ -7785,7 +7785,7 @@
         <v>6.300000190734863</v>
       </c>
       <c r="D455">
-        <v>3.588186740875244</v>
+        <v>4.254458427429199</v>
       </c>
     </row>
     <row r="456" spans="1:4">
@@ -7799,7 +7799,7 @@
         <v>-39.90000152587891</v>
       </c>
       <c r="D456">
-        <v>-23.3486213684082</v>
+        <v>-22.65341567993164</v>
       </c>
     </row>
     <row r="457" spans="1:4">
@@ -7813,7 +7813,7 @@
         <v>-4.300000190734863</v>
       </c>
       <c r="D457">
-        <v>-1.384016752243042</v>
+        <v>-1.341707110404968</v>
       </c>
     </row>
     <row r="458" spans="1:4">
@@ -7827,7 +7827,7 @@
         <v>-23.70000076293945</v>
       </c>
       <c r="D458">
-        <v>-18.19217681884766</v>
+        <v>-19.07578277587891</v>
       </c>
     </row>
     <row r="459" spans="1:4">
@@ -7841,7 +7841,7 @@
         <v>-1.299999952316284</v>
       </c>
       <c r="D459">
-        <v>-0.2120324969291687</v>
+        <v>-0.447931170463562</v>
       </c>
     </row>
     <row r="460" spans="1:4">
@@ -7855,7 +7855,7 @@
         <v>-10.5</v>
       </c>
       <c r="D460">
-        <v>1.069159507751465</v>
+        <v>0.519892692565918</v>
       </c>
     </row>
     <row r="461" spans="1:4">
@@ -7869,7 +7869,7 @@
         <v>6.400000095367432</v>
       </c>
       <c r="D461">
-        <v>6.383654594421387</v>
+        <v>4.477022171020508</v>
       </c>
     </row>
     <row r="462" spans="1:4">
@@ -7883,7 +7883,7 @@
         <v>-18.79999923706055</v>
       </c>
       <c r="D462">
-        <v>-16.60654067993164</v>
+        <v>-18.51052856445312</v>
       </c>
     </row>
     <row r="463" spans="1:4">
@@ -7897,7 +7897,7 @@
         <v>8.899999618530273</v>
       </c>
       <c r="D463">
-        <v>3.728381156921387</v>
+        <v>2.449880838394165</v>
       </c>
     </row>
     <row r="464" spans="1:4">
@@ -7911,7 +7911,7 @@
         <v>-0.2000000029802322</v>
       </c>
       <c r="D464">
-        <v>1.565611720085144</v>
+        <v>0.1029393374919891</v>
       </c>
     </row>
     <row r="465" spans="1:4">
@@ -7925,7 +7925,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D465">
-        <v>0.5846980810165405</v>
+        <v>0.6702061891555786</v>
       </c>
     </row>
     <row r="466" spans="1:4">
@@ -7939,7 +7939,7 @@
         <v>2</v>
       </c>
       <c r="D466">
-        <v>0.4888912439346313</v>
+        <v>0.4381009638309479</v>
       </c>
     </row>
     <row r="467" spans="1:4">
@@ -7953,7 +7953,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D467">
-        <v>-0.5648516416549683</v>
+        <v>0.3139729797840118</v>
       </c>
     </row>
     <row r="468" spans="1:4">
@@ -7967,7 +7967,7 @@
         <v>-11.60000038146973</v>
       </c>
       <c r="D468">
-        <v>-2.064594268798828</v>
+        <v>-4.8721022605896</v>
       </c>
     </row>
     <row r="469" spans="1:4">
@@ -7981,7 +7981,7 @@
         <v>-0.4000000059604645</v>
       </c>
       <c r="D469">
-        <v>0.7501355409622192</v>
+        <v>0.2890256941318512</v>
       </c>
     </row>
     <row r="470" spans="1:4">
@@ -7995,7 +7995,7 @@
         <v>-3.099999904632568</v>
       </c>
       <c r="D470">
-        <v>-1.875300049781799</v>
+        <v>-3.89409613609314</v>
       </c>
     </row>
     <row r="471" spans="1:4">
@@ -8009,7 +8009,7 @@
         <v>-10.89999961853027</v>
       </c>
       <c r="D471">
-        <v>-10.86273288726807</v>
+        <v>-9.404032707214355</v>
       </c>
     </row>
     <row r="472" spans="1:4">
@@ -8023,7 +8023,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D472">
-        <v>-3.978859424591064</v>
+        <v>-3.428076028823853</v>
       </c>
     </row>
     <row r="473" spans="1:4">
@@ -8037,7 +8037,7 @@
         <v>-1.5</v>
       </c>
       <c r="D473">
-        <v>2.206537246704102</v>
+        <v>0.9652199745178223</v>
       </c>
     </row>
     <row r="474" spans="1:4">
@@ -8051,7 +8051,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D474">
-        <v>0.4707483053207397</v>
+        <v>0.5640302896499634</v>
       </c>
     </row>
     <row r="475" spans="1:4">
@@ -8065,7 +8065,7 @@
         <v>-9.199999809265137</v>
       </c>
       <c r="D475">
-        <v>-6.631931304931641</v>
+        <v>-5.788080215454102</v>
       </c>
     </row>
     <row r="476" spans="1:4">
@@ -8079,7 +8079,7 @@
         <v>1</v>
       </c>
       <c r="D476">
-        <v>0.2944018244743347</v>
+        <v>0.06923338770866394</v>
       </c>
     </row>
     <row r="477" spans="1:4">
@@ -8093,7 +8093,7 @@
         <v>18.89999961853027</v>
       </c>
       <c r="D477">
-        <v>12.15747261047363</v>
+        <v>12.37560367584229</v>
       </c>
     </row>
     <row r="478" spans="1:4">
@@ -8107,7 +8107,7 @@
         <v>1.5</v>
       </c>
       <c r="D478">
-        <v>3.88785982131958</v>
+        <v>3.294674158096313</v>
       </c>
     </row>
     <row r="479" spans="1:4">
@@ -8121,7 +8121,7 @@
         <v>6.5</v>
       </c>
       <c r="D479">
-        <v>-0.3679254949092865</v>
+        <v>-1.258175015449524</v>
       </c>
     </row>
     <row r="480" spans="1:4">
@@ -8135,7 +8135,7 @@
         <v>-2</v>
       </c>
       <c r="D480">
-        <v>0.480291485786438</v>
+        <v>-0.1150499284267426</v>
       </c>
     </row>
     <row r="481" spans="1:4">
@@ -8149,7 +8149,7 @@
         <v>0.5</v>
       </c>
       <c r="D481">
-        <v>0.7899558544158936</v>
+        <v>0.4427706301212311</v>
       </c>
     </row>
     <row r="482" spans="1:4">
@@ -8163,7 +8163,7 @@
         <v>-3.099999904632568</v>
       </c>
       <c r="D482">
-        <v>0.6658614873886108</v>
+        <v>-0.02372154593467712</v>
       </c>
     </row>
     <row r="483" spans="1:4">
@@ -8177,7 +8177,7 @@
         <v>-24.79999923706055</v>
       </c>
       <c r="D483">
-        <v>-15.26623153686523</v>
+        <v>-16.13402557373047</v>
       </c>
     </row>
     <row r="484" spans="1:4">
@@ -8191,7 +8191,7 @@
         <v>-5.5</v>
       </c>
       <c r="D484">
-        <v>-3.69054651260376</v>
+        <v>-3.534772157669067</v>
       </c>
     </row>
     <row r="485" spans="1:4">
@@ -8205,7 +8205,7 @@
         <v>9.100000381469727</v>
       </c>
       <c r="D485">
-        <v>3.246114730834961</v>
+        <v>3.426715135574341</v>
       </c>
     </row>
     <row r="486" spans="1:4">
@@ -8219,7 +8219,7 @@
         <v>-5.5</v>
       </c>
       <c r="D486">
-        <v>-3.899268627166748</v>
+        <v>-3.951226949691772</v>
       </c>
     </row>
     <row r="487" spans="1:4">
@@ -8233,7 +8233,7 @@
         <v>-15</v>
       </c>
       <c r="D487">
-        <v>-8.798778533935547</v>
+        <v>-8.036055564880371</v>
       </c>
     </row>
     <row r="488" spans="1:4">
@@ -8247,7 +8247,7 @@
         <v>-1.200000047683716</v>
       </c>
       <c r="D488">
-        <v>-3.632240772247314</v>
+        <v>-4.481822490692139</v>
       </c>
     </row>
     <row r="489" spans="1:4">
@@ -8261,7 +8261,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D489">
-        <v>2.831658363342285</v>
+        <v>2.537548065185547</v>
       </c>
     </row>
     <row r="490" spans="1:4">
@@ -8275,7 +8275,7 @@
         <v>-0.800000011920929</v>
       </c>
       <c r="D490">
-        <v>0.429973304271698</v>
+        <v>-0.09785559773445129</v>
       </c>
     </row>
     <row r="491" spans="1:4">
@@ -8289,7 +8289,7 @@
         <v>10.39999961853027</v>
       </c>
       <c r="D491">
-        <v>1.735809922218323</v>
+        <v>2.119395971298218</v>
       </c>
     </row>
     <row r="492" spans="1:4">
@@ -8303,7 +8303,7 @@
         <v>-7.099999904632568</v>
       </c>
       <c r="D492">
-        <v>2.017289638519287</v>
+        <v>1.285256385803223</v>
       </c>
     </row>
     <row r="493" spans="1:4">
@@ -8317,7 +8317,7 @@
         <v>-12.19999980926514</v>
       </c>
       <c r="D493">
-        <v>-7.171858787536621</v>
+        <v>-8.225929260253906</v>
       </c>
     </row>
     <row r="494" spans="1:4">
@@ -8331,7 +8331,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D494">
-        <v>1.193041682243347</v>
+        <v>1.620163202285767</v>
       </c>
     </row>
     <row r="495" spans="1:4">
@@ -8345,7 +8345,7 @@
         <v>-16.39999961853027</v>
       </c>
       <c r="D495">
-        <v>0.1889078617095947</v>
+        <v>-3.789433240890503</v>
       </c>
     </row>
     <row r="496" spans="1:4">
@@ -8359,7 +8359,7 @@
         <v>6.900000095367432</v>
       </c>
       <c r="D496">
-        <v>1.679612755775452</v>
+        <v>1.087357878684998</v>
       </c>
     </row>
     <row r="497" spans="1:4">
@@ -8373,7 +8373,7 @@
         <v>7.400000095367432</v>
       </c>
       <c r="D497">
-        <v>4.122384548187256</v>
+        <v>4.112765312194824</v>
       </c>
     </row>
     <row r="498" spans="1:4">
@@ -8387,7 +8387,7 @@
         <v>1.5</v>
       </c>
       <c r="D498">
-        <v>-2.771138668060303</v>
+        <v>-0.501716673374176</v>
       </c>
     </row>
     <row r="499" spans="1:4">
@@ -8401,7 +8401,7 @@
         <v>-12.60000038146973</v>
       </c>
       <c r="D499">
-        <v>-7.486769676208496</v>
+        <v>-8.511656761169434</v>
       </c>
     </row>
     <row r="500" spans="1:4">
@@ -8415,7 +8415,7 @@
         <v>-0.800000011920929</v>
       </c>
       <c r="D500">
-        <v>-2.337579727172852</v>
+        <v>-1.931820511817932</v>
       </c>
     </row>
     <row r="501" spans="1:4">
@@ -8429,7 +8429,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D501">
-        <v>-0.06857335567474365</v>
+        <v>-0.4549959897994995</v>
       </c>
     </row>
     <row r="502" spans="1:4">
@@ -8443,7 +8443,7 @@
         <v>-7.400000095367432</v>
       </c>
       <c r="D502">
-        <v>-5.698195457458496</v>
+        <v>-5.696498394012451</v>
       </c>
     </row>
     <row r="503" spans="1:4">
@@ -8457,7 +8457,7 @@
         <v>-3.700000047683716</v>
       </c>
       <c r="D503">
-        <v>-0.3237349390983582</v>
+        <v>-2.081682205200195</v>
       </c>
     </row>
     <row r="504" spans="1:4">
@@ -8471,7 +8471,7 @@
         <v>7.599999904632568</v>
       </c>
       <c r="D504">
-        <v>2.746252536773682</v>
+        <v>2.103847026824951</v>
       </c>
     </row>
     <row r="505" spans="1:4">
@@ -8485,7 +8485,7 @@
         <v>-13.60000038146973</v>
       </c>
       <c r="D505">
-        <v>-7.823537349700928</v>
+        <v>-8.939820289611816</v>
       </c>
     </row>
     <row r="506" spans="1:4">
@@ -8499,7 +8499,7 @@
         <v>6.400000095367432</v>
       </c>
       <c r="D506">
-        <v>11.60318183898926</v>
+        <v>11.14647960662842</v>
       </c>
     </row>
     <row r="507" spans="1:4">
@@ -8513,7 +8513,7 @@
         <v>-12.60000038146973</v>
       </c>
       <c r="D507">
-        <v>-3.827857971191406</v>
+        <v>-5.154051780700684</v>
       </c>
     </row>
     <row r="508" spans="1:4">
@@ -8527,7 +8527,7 @@
         <v>-10.60000038146973</v>
       </c>
       <c r="D508">
-        <v>-8.20728588104248</v>
+        <v>-9.088973999023438</v>
       </c>
     </row>
     <row r="509" spans="1:4">
@@ -8541,7 +8541,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D509">
-        <v>2.095200538635254</v>
+        <v>2.140170335769653</v>
       </c>
     </row>
     <row r="510" spans="1:4">
@@ -8555,7 +8555,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D510">
-        <v>3.061156749725342</v>
+        <v>2.048512697219849</v>
       </c>
     </row>
     <row r="511" spans="1:4">
@@ -8569,7 +8569,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D511">
-        <v>-1.554677248001099</v>
+        <v>-1.954736471176147</v>
       </c>
     </row>
     <row r="512" spans="1:4">
@@ -8583,7 +8583,7 @@
         <v>-0.4000000059604645</v>
       </c>
       <c r="D512">
-        <v>-1.133896470069885</v>
+        <v>-1.087728381156921</v>
       </c>
     </row>
     <row r="513" spans="1:4">
@@ -8597,7 +8597,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D513">
-        <v>0.02189177274703979</v>
+        <v>-0.7941271662712097</v>
       </c>
     </row>
     <row r="514" spans="1:4">
@@ -8611,7 +8611,7 @@
         <v>-1</v>
       </c>
       <c r="D514">
-        <v>-3.007039070129395</v>
+        <v>-4.701650619506836</v>
       </c>
     </row>
     <row r="515" spans="1:4">
@@ -8625,7 +8625,7 @@
         <v>-6.199999809265137</v>
       </c>
       <c r="D515">
-        <v>-2.283638000488281</v>
+        <v>-3.233603954315186</v>
       </c>
     </row>
     <row r="516" spans="1:4">
@@ -8639,7 +8639,7 @@
         <v>-6.099999904632568</v>
       </c>
       <c r="D516">
-        <v>-0.7774603366851807</v>
+        <v>-0.9012232422828674</v>
       </c>
     </row>
     <row r="517" spans="1:4">
@@ -8653,7 +8653,7 @@
         <v>-4.400000095367432</v>
       </c>
       <c r="D517">
-        <v>-1.617861151695251</v>
+        <v>-1.107615351676941</v>
       </c>
     </row>
     <row r="518" spans="1:4">
@@ -8667,7 +8667,7 @@
         <v>-3.400000095367432</v>
       </c>
       <c r="D518">
-        <v>0.5180743932723999</v>
+        <v>-0.04906389117240906</v>
       </c>
     </row>
     <row r="519" spans="1:4">
@@ -8681,7 +8681,7 @@
         <v>-7.900000095367432</v>
       </c>
       <c r="D519">
-        <v>-4.44119930267334</v>
+        <v>-4.225555419921875</v>
       </c>
     </row>
     <row r="520" spans="1:4">
@@ -8695,7 +8695,7 @@
         <v>-8</v>
       </c>
       <c r="D520">
-        <v>1.180638790130615</v>
+        <v>0.04520514607429504</v>
       </c>
     </row>
     <row r="521" spans="1:4">
@@ -8709,7 +8709,7 @@
         <v>-5.599999904632568</v>
       </c>
       <c r="D521">
-        <v>1.775826096534729</v>
+        <v>0.2427299320697784</v>
       </c>
     </row>
     <row r="522" spans="1:4">
@@ -8723,7 +8723,7 @@
         <v>-2.700000047683716</v>
       </c>
       <c r="D522">
-        <v>-7.564745903015137</v>
+        <v>-6.14453125</v>
       </c>
     </row>
     <row r="523" spans="1:4">
@@ -8737,7 +8737,7 @@
         <v>-6.599999904632568</v>
       </c>
       <c r="D523">
-        <v>-6.697139739990234</v>
+        <v>-7.580371856689453</v>
       </c>
     </row>
     <row r="524" spans="1:4">
@@ -8751,7 +8751,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D524">
-        <v>0.4962431192398071</v>
+        <v>0.1823860704898834</v>
       </c>
     </row>
     <row r="525" spans="1:4">
@@ -8765,7 +8765,7 @@
         <v>9.399999618530273</v>
       </c>
       <c r="D525">
-        <v>5.050311088562012</v>
+        <v>5.858315944671631</v>
       </c>
     </row>
     <row r="526" spans="1:4">
@@ -8779,7 +8779,7 @@
         <v>-9.199999809265137</v>
       </c>
       <c r="D526">
-        <v>1.346990346908569</v>
+        <v>0.5598324537277222</v>
       </c>
     </row>
     <row r="527" spans="1:4">
@@ -8793,7 +8793,7 @@
         <v>-14</v>
       </c>
       <c r="D527">
-        <v>-15.56772613525391</v>
+        <v>-18.07782745361328</v>
       </c>
     </row>
     <row r="528" spans="1:4">
@@ -8807,7 +8807,7 @@
         <v>-12.89999961853027</v>
       </c>
       <c r="D528">
-        <v>-8.086797714233398</v>
+        <v>-9.219505310058594</v>
       </c>
     </row>
     <row r="529" spans="1:4">
@@ -8821,7 +8821,7 @@
         <v>-3.200000047683716</v>
       </c>
       <c r="D529">
-        <v>-3.519235134124756</v>
+        <v>-2.304657697677612</v>
       </c>
     </row>
     <row r="530" spans="1:4">
@@ -8835,7 +8835,7 @@
         <v>-3.5</v>
       </c>
       <c r="D530">
-        <v>0.5414649248123169</v>
+        <v>0.7265353202819824</v>
       </c>
     </row>
     <row r="531" spans="1:4">
@@ -8849,7 +8849,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D531">
-        <v>0.5675207376480103</v>
+        <v>0.1711308062076569</v>
       </c>
     </row>
     <row r="532" spans="1:4">
@@ -8863,7 +8863,7 @@
         <v>-12.39999961853027</v>
       </c>
       <c r="D532">
-        <v>-9.626569747924805</v>
+        <v>-9.377376556396484</v>
       </c>
     </row>
     <row r="533" spans="1:4">
@@ -8877,7 +8877,7 @@
         <v>-10.10000038146973</v>
       </c>
       <c r="D533">
-        <v>-5.866507530212402</v>
+        <v>-6.073144435882568</v>
       </c>
     </row>
     <row r="534" spans="1:4">
@@ -8891,7 +8891,7 @@
         <v>-26</v>
       </c>
       <c r="D534">
-        <v>-21.68647575378418</v>
+        <v>-20.37236022949219</v>
       </c>
     </row>
     <row r="535" spans="1:4">
@@ -8905,7 +8905,7 @@
         <v>19.79999923706055</v>
       </c>
       <c r="D535">
-        <v>15.62192153930664</v>
+        <v>14.49450874328613</v>
       </c>
     </row>
     <row r="536" spans="1:4">
@@ -8919,7 +8919,7 @@
         <v>-2</v>
       </c>
       <c r="D536">
-        <v>1.965736269950867</v>
+        <v>0.6934176683425903</v>
       </c>
     </row>
     <row r="537" spans="1:4">
@@ -8933,7 +8933,7 @@
         <v>-2.5</v>
       </c>
       <c r="D537">
-        <v>-1.429681897163391</v>
+        <v>-2.367020845413208</v>
       </c>
     </row>
     <row r="538" spans="1:4">
@@ -8947,7 +8947,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D538">
-        <v>1.41731870174408</v>
+        <v>0.5979726314544678</v>
       </c>
     </row>
     <row r="539" spans="1:4">
@@ -8961,7 +8961,7 @@
         <v>-7.800000190734863</v>
       </c>
       <c r="D539">
-        <v>-6.580421447753906</v>
+        <v>-7.710746288299561</v>
       </c>
     </row>
     <row r="540" spans="1:4">
@@ -8975,7 +8975,7 @@
         <v>-13</v>
       </c>
       <c r="D540">
-        <v>-8.884632110595703</v>
+        <v>-9.413979530334473</v>
       </c>
     </row>
     <row r="541" spans="1:4">
@@ -8989,7 +8989,7 @@
         <v>11.89999961853027</v>
       </c>
       <c r="D541">
-        <v>3.278058052062988</v>
+        <v>3.247954368591309</v>
       </c>
     </row>
     <row r="542" spans="1:4">
@@ -9003,7 +9003,7 @@
         <v>-7.900000095367432</v>
       </c>
       <c r="D542">
-        <v>-4.259121417999268</v>
+        <v>-5.57705020904541</v>
       </c>
     </row>
     <row r="543" spans="1:4">
@@ -9017,7 +9017,7 @@
         <v>15.19999980926514</v>
       </c>
       <c r="D543">
-        <v>12.96696472167969</v>
+        <v>11.10247802734375</v>
       </c>
     </row>
     <row r="544" spans="1:4">
@@ -9031,7 +9031,7 @@
         <v>7</v>
       </c>
       <c r="D544">
-        <v>12.97065734863281</v>
+        <v>10.9127311706543</v>
       </c>
     </row>
     <row r="545" spans="1:4">
@@ -9045,7 +9045,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D545">
-        <v>-0.6572477221488953</v>
+        <v>-0.3236386477947235</v>
       </c>
     </row>
     <row r="546" spans="1:4">
@@ -9059,7 +9059,7 @@
         <v>-2.099999904632568</v>
       </c>
       <c r="D546">
-        <v>1.390496850013733</v>
+        <v>-2.065155982971191</v>
       </c>
     </row>
     <row r="547" spans="1:4">
@@ -9073,7 +9073,7 @@
         <v>5.900000095367432</v>
       </c>
       <c r="D547">
-        <v>-0.3787286877632141</v>
+        <v>-0.6115580797195435</v>
       </c>
     </row>
     <row r="548" spans="1:4">
@@ -9087,7 +9087,7 @@
         <v>-3.599999904632568</v>
       </c>
       <c r="D548">
-        <v>-5.033945083618164</v>
+        <v>-4.507481098175049</v>
       </c>
     </row>
     <row r="549" spans="1:4">
@@ -9101,7 +9101,7 @@
         <v>-6.900000095367432</v>
       </c>
       <c r="D549">
-        <v>-0.08855557441711426</v>
+        <v>-1.442567229270935</v>
       </c>
     </row>
     <row r="550" spans="1:4">
@@ -9115,7 +9115,7 @@
         <v>-6.699999809265137</v>
       </c>
       <c r="D550">
-        <v>-6.568019390106201</v>
+        <v>-8.441712379455566</v>
       </c>
     </row>
     <row r="551" spans="1:4">
@@ -9129,7 +9129,7 @@
         <v>-17.20000076293945</v>
       </c>
       <c r="D551">
-        <v>-12.03931427001953</v>
+        <v>-16.6697883605957</v>
       </c>
     </row>
     <row r="552" spans="1:4">
@@ -9143,7 +9143,7 @@
         <v>-5.900000095367432</v>
       </c>
       <c r="D552">
-        <v>-4.359776973724365</v>
+        <v>-4.938905239105225</v>
       </c>
     </row>
   </sheetData>
